--- a/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
+++ b/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
@@ -285,6 +285,18 @@
     <t xml:space="preserve">Internet Retail</t>
   </si>
   <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Visa</t>
+  </si>
+  <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit Services</t>
+  </si>
+  <si>
     <t>PANW</t>
   </si>
   <si>
@@ -304,18 +316,6 @@
   </si>
   <si>
     <t xml:space="preserve">Software - Application</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Visa</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit Services</t>
   </si>
   <si>
     <t>NKE</t>
@@ -1047,8 +1047,9 @@
     <col bestFit="1" min="2" max="2" width="28.140625"/>
     <col bestFit="1" min="3" max="3" width="21.7109375"/>
     <col bestFit="1" min="4" max="4" width="33.8515625"/>
-    <col bestFit="1" min="5" max="5" width="6.421875"/>
+    <col customWidth="1" min="5" max="5" width="8.140625"/>
     <col bestFit="1" min="6" max="6" width="10.140625"/>
+    <col customWidth="1" min="7" max="7" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -1703,88 +1704,88 @@
         <v>90</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="E29" s="3">
-        <v>1.2198249976658535e-02</v>
+        <v>1.5924694893597595e-02</v>
       </c>
       <c r="F29" s="4">
         <v>2.e-02</v>
       </c>
       <c r="G29" s="1">
-        <v>0.37641799770710743</v>
+        <v>2.5593149997167481</v>
       </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E30" s="3">
-        <v>1.1098145244875833e-02</v>
+        <v>1.2198249976658535e-02</v>
       </c>
       <c r="F30" s="4">
         <v>2.e-02</v>
       </c>
       <c r="G30" s="1">
-        <v>1.2999238318426021</v>
+        <v>0.37641799770710743</v>
       </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="E31" s="3">
-        <v>8.6036655312242694e-03</v>
+        <v>1.1098145244875833e-02</v>
       </c>
       <c r="F31" s="4">
         <v>2.e-02</v>
       </c>
       <c r="G31" s="1">
-        <v>0.14067084935828603</v>
+        <v>1.2999238318426021</v>
       </c>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E32" s="3">
-        <v>1.5924694893597595e-02</v>
+        <v>8.6036655312242694e-03</v>
       </c>
       <c r="F32" s="4">
         <v>2.e-02</v>
       </c>
       <c r="G32" s="1">
-        <v>2.5593149997167481</v>
+        <v>0.14067084935828603</v>
       </c>
     </row>
     <row r="33" ht="14.25">
@@ -1887,7 +1888,7 @@
         <v>111</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>112</v>
@@ -1913,7 +1914,7 @@
         <v>30</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E38" s="3">
         <v>1.4464766120519525e-02</v>
@@ -1936,7 +1937,7 @@
         <v>30</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E39" s="3">
         <v>1.3998904335095513e-02</v>
@@ -2292,10 +2293,10 @@
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2347,10 +2348,10 @@
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C10" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2358,10 +2359,10 @@
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C11" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2369,10 +2370,10 @@
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="8" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C12" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2820,7 +2821,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" id="{00340062-0056-4313-B5B4-00B800F100EE}">
+          <x14:cfRule type="containsText" priority="1" id="{001900C0-003B-4FB2-8F8A-001800C700C9}">
             <xm:f>NOT(ISERROR(SEARCH("$J$5",I2)))</xm:f>
             <xm:f>$J$5</xm:f>
             <x14:dxf>
@@ -4267,16 +4268,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E38" s="3">
         <v>1.5924694893597595e-02</v>
@@ -4311,7 +4312,7 @@
         <v>111</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
         <v>112</v>
@@ -4352,7 +4353,7 @@
         <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E40" s="3">
         <v>1.4464766120519525e-02</v>
@@ -4390,7 +4391,7 @@
         <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E41" s="3">
         <v>1.3998904335095513e-02</v>
@@ -4495,10 +4496,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
         <v>30</v>
@@ -4571,10 +4572,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
@@ -4609,16 +4610,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
         <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E47" s="3">
         <v>8.6036655312242694e-03</v>
@@ -4810,7 +4811,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{00A9000E-0075-488B-B4A7-001000040039}">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{004C0067-00BA-47A4-AAD3-00590047001C}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4827,7 +4828,7 @@
           <xm:sqref>G2:G51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{001600A1-0042-4AED-927E-00B600680097}">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{009E0047-0075-4B53-9EB3-005C001B0084}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4844,7 +4845,7 @@
           <xm:sqref>H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{005F00E4-0082-4B43-AED1-00A700F2004C}">
+          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{004400C0-00FD-45F3-B233-007900CB004C}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4861,7 +4862,7 @@
           <xm:sqref>G2:G51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{0039000E-0004-4DC4-9306-009D00B20028}">
+          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{00D90051-0000-4FD4-9189-005E00AA0095}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4878,7 +4879,7 @@
           <xm:sqref>H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" id="{009F00DE-00CE-4F4F-A302-00FF004D0043}">
+          <x14:cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" id="{008B000F-005D-4418-B25A-0090009200FB}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -4895,7 +4896,7 @@
           <xm:sqref>J2:J51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="lessThan" id="{00CE00FF-00DC-4DD5-A2B7-009D000A000B}">
+          <x14:cfRule type="cellIs" priority="7" operator="lessThan" id="{00120069-0055-4B80-ACF4-00DF002C004B}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -4912,7 +4913,7 @@
           <xm:sqref>J2:J51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" id="{00050071-000D-40B5-B1BC-000600EE0048}">
+          <x14:cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" id="{001600CF-0075-4413-B998-0061002C0010}">
             <xm:f>1</xm:f>
             <x14:dxf>
               <font>
@@ -4929,7 +4930,7 @@
           <xm:sqref>K2:K51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{003400CA-0034-445F-AB26-001F00C90009}">
+          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{006A00EF-00C3-4D3F-810F-00C300F50023}">
             <xm:f>1</xm:f>
             <x14:dxf>
               <font>
@@ -4946,7 +4947,7 @@
           <xm:sqref>K2:K51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{005E0056-0082-4D66-AC5B-00DC00C3007E}">
+          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{00630049-00A8-49AA-9BEF-00FB007400DE}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -4963,7 +4964,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" id="{005400DB-00A7-4040-A742-009D0036000C}">
+          <x14:cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" id="{00810061-00AD-4EFD-981D-000700F4001B}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -4980,7 +4981,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" id="{00880078-00B8-41B9-9D70-006600B30098}">
+          <x14:cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" id="{00A5002C-0065-4E7D-9CE4-00AD00E200FD}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -4997,7 +4998,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{004300E8-0095-42A0-AE0F-004B00B0008A}">
+          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{00890047-00F5-467A-8F1B-00480097005C}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>

--- a/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
+++ b/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
@@ -7,16 +7,18 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Portfolio_Stocks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BBPTACShadowWks0001" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Portfolio_Stocks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="BBPTACShadowWks0001" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t>YahooTicker</t>
   </si>
@@ -36,423 +38,435 @@
     <t>adj_weight</t>
   </si>
   <si>
+    <t>adj_weight_GBP</t>
+  </si>
+  <si>
+    <t>inv_vol_GBP</t>
+  </si>
+  <si>
+    <t>CNR.TO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canadian National Railway</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Railroads</t>
+  </si>
+  <si>
+    <t>AZN.L</t>
+  </si>
+  <si>
+    <t>AstraZeneca</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drug Manufacturers—General</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Corp</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>NESN.SW</t>
+  </si>
+  <si>
+    <t>Nestle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer Defensive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packaged Foods</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>Costco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discount Stores</t>
+  </si>
+  <si>
+    <t>MC.PA</t>
+  </si>
+  <si>
+    <t>LVMH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer Cyclical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxury Goods</t>
+  </si>
+  <si>
+    <t>9984.T</t>
+  </si>
+  <si>
+    <t>SoftBank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telecom Services</t>
+  </si>
+  <si>
+    <t>MRNA</t>
+  </si>
+  <si>
+    <t>Moderna</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>JNJ</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Procter &amp; Gamble Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>WM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waste Management</t>
+  </si>
+  <si>
+    <t>SMT.L</t>
+  </si>
+  <si>
+    <t>SMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investment Trust</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Deere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm &amp; Heavy Construction Machinery</t>
+  </si>
+  <si>
+    <t>FAS.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Asian</t>
+  </si>
+  <si>
+    <t>HVPE.L</t>
+  </si>
+  <si>
+    <t>HarbourVest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private Equity</t>
+  </si>
+  <si>
+    <t>LIN</t>
+  </si>
+  <si>
+    <t>Linde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic Materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialty Chemicals</t>
+  </si>
+  <si>
+    <t>TMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermo Fisher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnostics &amp; Research</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Visa</t>
+  </si>
+  <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit Services</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novo Nordisk</t>
+  </si>
+  <si>
+    <t>ECL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecolab Inc.</t>
+  </si>
+  <si>
+    <t>ABBV</t>
+  </si>
+  <si>
+    <t>Abbvie</t>
+  </si>
+  <si>
+    <t>DG.PA</t>
+  </si>
+  <si>
+    <t>VINCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>JPM</t>
+  </si>
+  <si>
+    <t>JPMorgan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banks - Diversified</t>
+  </si>
+  <si>
+    <t>SMSN.IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Electronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer Electronics</t>
+  </si>
+  <si>
+    <t>XOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exxon Mobil Corporation</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oil &amp; Gas Integrated</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estee Lauder</t>
+  </si>
+  <si>
+    <t>NKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIKE, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old Dominion Freight Line, Inc.</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet Retail</t>
+  </si>
+  <si>
+    <t>RIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rio Tinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Industrial Metals &amp; Mining</t>
+  </si>
+  <si>
+    <t>BHP</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>Albemarle</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t>Toyota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>HON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honeywell International</t>
+  </si>
+  <si>
+    <t>Conglomerates</t>
+  </si>
+  <si>
+    <t>SHW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sherwin-Williams Company</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alphabet Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet Content &amp; Information</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software - Application</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lam Research Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>MELI</t>
+  </si>
+  <si>
+    <t>MercadoLibre</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>III.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3i Group</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>ServiceNow</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials, Inc.</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>HubSpot</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>CrowdStrike</t>
+  </si>
+  <si>
+    <t>NIO</t>
+  </si>
+  <si>
+    <t>Nio</t>
+  </si>
+  <si>
+    <t>asset</t>
+  </si>
+  <si>
+    <t>port_inverse_vol_GBP</t>
+  </si>
+  <si>
+    <t>Adjusted_weight</t>
+  </si>
+  <si>
     <t>weight_market_cap</t>
   </si>
   <si>
-    <t>CNR.TO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canadian National Railway</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Railroads</t>
-  </si>
-  <si>
-    <t>MRNA</t>
-  </si>
-  <si>
-    <t>Moderna</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>AZN.L</t>
-  </si>
-  <si>
-    <t>AstraZeneca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drug Manufacturers—General</t>
-  </si>
-  <si>
-    <t>NESN.SW</t>
-  </si>
-  <si>
-    <t>Nestle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Defensive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packaged Foods</t>
-  </si>
-  <si>
-    <t>JNJ</t>
-  </si>
-  <si>
-    <t>Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drug Manufacturers - General</t>
-  </si>
-  <si>
-    <t>SMT.L</t>
-  </si>
-  <si>
-    <t>SMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investment Trust</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Electronics</t>
-  </si>
-  <si>
-    <t>9984.T</t>
-  </si>
-  <si>
-    <t>SoftBank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telecom Services</t>
-  </si>
-  <si>
-    <t>PG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Procter &amp; Gamble Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>LIN</t>
-  </si>
-  <si>
-    <t>Linde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic Materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specialty Chemicals</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>WM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waste Management</t>
-  </si>
-  <si>
-    <t>NVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novo Nordisk</t>
-  </si>
-  <si>
-    <t>ECL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecolab Inc.</t>
-  </si>
-  <si>
-    <t>SHW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sherwin-Williams Company</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>Costco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount Stores</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old Dominion Freight Line, Inc.</t>
-  </si>
-  <si>
-    <t>Trucking</t>
-  </si>
-  <si>
-    <t>FAS.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Asian</t>
-  </si>
-  <si>
-    <t>EL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estee Lauder</t>
-  </si>
-  <si>
-    <t>DG.PA</t>
-  </si>
-  <si>
-    <t>VINCI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>TMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thermo Fisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnostics &amp; Research</t>
-  </si>
-  <si>
-    <t>TM</t>
-  </si>
-  <si>
-    <t>Toyota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Cyclical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto Manufacturers</t>
-  </si>
-  <si>
-    <t>XOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exxon Mobil Corporation</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oil &amp; Gas Integrated</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>Deere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farm &amp; Heavy Construction Machinery</t>
-  </si>
-  <si>
-    <t>MC.PA</t>
-  </si>
-  <si>
-    <t>LVMH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxury Goods</t>
-  </si>
-  <si>
-    <t>ALB</t>
-  </si>
-  <si>
-    <t>Albemarle</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internet Retail</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Visa</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit Services</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto</t>
-  </si>
-  <si>
-    <t>ABBV</t>
-  </si>
-  <si>
-    <t>Abbvie</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>HubSpot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software - Application</t>
-  </si>
-  <si>
-    <t>NKE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIKE, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Footwear &amp; Accessories</t>
-  </si>
-  <si>
-    <t>BHP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Industrial Metals &amp; Mining</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alphabet Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internet Content &amp; Information</t>
-  </si>
-  <si>
-    <t>RIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rio Tinto</t>
-  </si>
-  <si>
-    <t>JPM</t>
-  </si>
-  <si>
-    <t>JPMorgan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banks - Diversified</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>ServiceNow</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>Tesla</t>
-  </si>
-  <si>
-    <t>SMSN.IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Electronics</t>
-  </si>
-  <si>
-    <t>III.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3i Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private Equity</t>
-  </si>
-  <si>
-    <t>HON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honeywell International</t>
-  </si>
-  <si>
-    <t>Conglomerates</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials, Inc.</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lam Research Corporation</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>NVIDIA</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>HVPE.L</t>
-  </si>
-  <si>
-    <t>HarbourVest</t>
-  </si>
-  <si>
-    <t>MELI</t>
-  </si>
-  <si>
-    <t>MercadoLibre</t>
-  </si>
-  <si>
-    <t>NIO</t>
-  </si>
-  <si>
-    <t>Nio</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>CrowdStrike</t>
-  </si>
-  <si>
-    <t>Adjusted_weight</t>
-  </si>
-  <si>
     <t>Valuation_Score_final</t>
   </si>
   <si>
@@ -469,14 +483,18 @@
   </si>
   <si>
     <t>cagr</t>
+  </si>
+  <si>
+    <t>Unclassified</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="160" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="160" formatCode="0.0000%"/>
+    <numFmt numFmtId="161" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -521,20 +539,20 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="1" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="160" xfId="1" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="1" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="1" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="160" xfId="1" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="161" xfId="1" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="160" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="160" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="161" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="161" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1044,12 +1062,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
+    <col bestFit="1" min="1" max="1" width="11.140625"/>
     <col bestFit="1" min="2" max="2" width="28.140625"/>
     <col bestFit="1" min="3" max="3" width="21.7109375"/>
     <col bestFit="1" min="4" max="4" width="33.8515625"/>
     <col customWidth="1" min="5" max="5" width="8.140625"/>
     <col bestFit="1" min="6" max="6" width="10.140625"/>
-    <col customWidth="1" min="7" max="7" width="9.140625"/>
+    <col bestFit="1" min="7" max="7" width="14.7109375"/>
+    <col bestFit="1" min="8" max="8" width="11.421875"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -1068,264 +1088,300 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3">
         <v>3.0962634061024067e-02</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>5.9999999999999998e-02</v>
       </c>
-      <c r="G2" s="1">
-        <v>0.41723862140173806</v>
+      <c r="G2" s="4">
+        <v>4.0000000000000001e-02</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.7134502405334247e-02</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3">
-        <v>7.2822559543963706e-03</v>
-      </c>
-      <c r="F3" s="4">
-        <v>5.0000000000000003e-02</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.26560055421124462</v>
+        <v>3.1424819508328677e-02</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="G3" s="4">
+        <v>4.0000000000000001e-02</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2.5833436819371197e-02</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="3">
-        <v>3.1424819508328677e-02</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2.9999999999999999e-02</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.2206489506814897</v>
+        <v>2.4805671292413338e-02</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.5000000000000001e-02</v>
+      </c>
+      <c r="G4" s="4">
+        <v>4.0000000000000001e-02</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2.1015659879092135e-02</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <v>3.052356663662641e-02</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>2.9999999999999999e-02</v>
       </c>
-      <c r="G5" s="1">
-        <v>1.7219006596046309</v>
+      <c r="G5" s="4">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3.4702113934566049e-02</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>3.0292282855981574e-02</v>
-      </c>
-      <c r="F6" s="4">
+        <v>2.8815825506352546e-02</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G6" s="4">
         <v>2.9999999999999999e-02</v>
       </c>
-      <c r="G6" s="1">
-        <v>2.2112144227478443</v>
+      <c r="H6" s="5">
+        <v>2.5045730085698558e-02</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E7" s="3">
-        <v>2.7534380619805943e-02</v>
-      </c>
-      <c r="F7" s="4">
+        <v>2.0270896772761948e-02</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G7" s="4">
         <v>2.9999999999999999e-02</v>
       </c>
-      <c r="G7" s="1">
-        <v>6.5100912489591004e-02</v>
+      <c r="H7" s="5">
+        <v>2.2364703842172446e-02</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E8" s="3">
-        <v>2.2977675579801321e-02</v>
-      </c>
-      <c r="F8" s="4">
+        <v>1.8889675597916298e-02</v>
+      </c>
+      <c r="F8" s="3">
         <v>2.9999999999999999e-02</v>
       </c>
-      <c r="G8" s="1">
-        <v>15.404678289461771</v>
+      <c r="G8" s="4">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1.5717863088204321e-02</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3">
-        <v>1.8889675597916298e-02</v>
-      </c>
-      <c r="F9" s="4">
+        <v>7.2822559543963706e-03</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5.0000000000000003e-02</v>
+      </c>
+      <c r="G9" s="4">
         <v>2.9999999999999999e-02</v>
       </c>
-      <c r="G9" s="1">
-        <v>0.33850554930938703</v>
+      <c r="H9" s="5">
+        <v>8.0822989818199395e-03</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10" s="3">
-        <v>2.7132928626070054e-02</v>
-      </c>
-      <c r="F10" s="4">
+        <v>3.0292282855981574e-02</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="G10" s="4">
         <v>2.5000000000000001e-02</v>
       </c>
-      <c r="G10" s="1">
-        <v>1.8491420533615384</v>
+      <c r="H10" s="5">
+        <v>2.9830450923956489e-02</v>
       </c>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" s="3">
-        <v>2.5899480754485733e-02</v>
-      </c>
-      <c r="F11" s="4">
+        <v>2.7132928626070054e-02</v>
+      </c>
+      <c r="F11" s="3">
         <v>2.5000000000000001e-02</v>
       </c>
-      <c r="G11" s="1">
-        <v>0.96306077004919688</v>
+      <c r="G11" s="4">
+        <v>2.5000000000000001e-02</v>
+      </c>
+      <c r="H11" s="5">
+        <v>2.8788334737737748e-02</v>
       </c>
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="3">
-        <v>2.4805671292413338e-02</v>
-      </c>
-      <c r="F12" s="4">
+        <v>2.339145668227165e-02</v>
+      </c>
+      <c r="F12" s="3">
         <v>2.5000000000000001e-02</v>
       </c>
-      <c r="G12" s="1">
-        <v>13.469496343266824</v>
+      <c r="G12" s="4">
+        <v>2.5000000000000001e-02</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2.8352089725409115e-02</v>
       </c>
     </row>
     <row r="13" ht="14.25">
@@ -1336,801 +1392,906 @@
         <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3">
-        <v>2.339145668227165e-02</v>
-      </c>
-      <c r="F13" s="4">
+        <v>2.7534380619805943e-02</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="G13" s="4">
         <v>2.5000000000000001e-02</v>
       </c>
-      <c r="G13" s="1">
-        <v>0.36198835859925893</v>
+      <c r="H13" s="5">
+        <v>2.0829207947211357e-02</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E14" s="3">
-        <v>3.3426578117660671e-02</v>
+        <v>2.1699035796102186e-02</v>
       </c>
       <c r="F14" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G14" s="1">
-        <v>1.903157975691689</v>
+      <c r="G14" s="4">
+        <v>2.5000000000000001e-02</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1.928301982771527e-02</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3">
-        <v>2.9899510066812067e-02</v>
-      </c>
-      <c r="F15" s="4">
+        <v>2.4002268007459516e-02</v>
+      </c>
+      <c r="F15" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G15" s="1">
-        <v>0.26732894581593292</v>
+      <c r="G15" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H15" s="5">
+        <v>3.206075137216953e-02</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E16" s="3">
-        <v>2.9175859286267512e-02</v>
-      </c>
-      <c r="F16" s="4">
+        <v>1.20868276388375e-02</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1.e-02</v>
+      </c>
+      <c r="G16" s="4">
         <v>2.e-02</v>
       </c>
-      <c r="G16" s="1">
-        <v>0.33656287556663184</v>
+      <c r="H16" s="5">
+        <v>2.4499003248388124e-02</v>
       </c>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3">
-        <v>2.8815825506352546e-02</v>
-      </c>
-      <c r="F17" s="4">
+        <v>2.5899480754485733e-02</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.5000000000000001e-02</v>
+      </c>
+      <c r="G17" s="4">
         <v>2.e-02</v>
       </c>
-      <c r="G17" s="1">
-        <v>1.2297858457118869</v>
+      <c r="H17" s="5">
+        <v>2.374164343461406e-02</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3">
-        <v>2.7878086561949296e-02</v>
-      </c>
-      <c r="F18" s="4">
+        <v>2.2745125426314856e-02</v>
+      </c>
+      <c r="F18" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G18" s="1">
-        <v>0.18624571141642482</v>
+      <c r="G18" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H18" s="5">
+        <v>2.3089961559775309e-02</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3">
-        <v>2.4002268007459516e-02</v>
-      </c>
-      <c r="F19" s="4">
+        <v>1.5924694893597595e-02</v>
+      </c>
+      <c r="F19" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G19" s="1">
-        <v>2.5255517909205934e-03</v>
+      <c r="G19" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H19" s="5">
+        <v>2.2524399757407488e-02</v>
       </c>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" s="3">
-        <v>2.3529974058399253e-02</v>
-      </c>
-      <c r="F20" s="4">
+        <v>3.3426578117660671e-02</v>
+      </c>
+      <c r="F20" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G20" s="1">
-        <v>0.34937435560550667</v>
+      <c r="G20" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H20" s="5">
+        <v>2.245773102572042e-02</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3">
-        <v>2.2837587441750774e-02</v>
-      </c>
-      <c r="F21" s="4">
+        <v>2.9899510066812067e-02</v>
+      </c>
+      <c r="F21" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G21" s="1">
-        <v>0.35090715016248641</v>
+      <c r="G21" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H21" s="5">
+        <v>2.2136447362695606e-02</v>
       </c>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="E22" s="3">
-        <v>2.2745125426314856e-02</v>
-      </c>
-      <c r="F22" s="4">
+        <v>1.1098145244875833e-02</v>
+      </c>
+      <c r="F22" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G22" s="1">
-        <v>1.0754326660837144</v>
+      <c r="G22" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H22" s="5">
+        <v>2.2106707876867186e-02</v>
       </c>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E23" s="3">
-        <v>2.2384977711044654e-02</v>
-      </c>
-      <c r="F23" s="4">
+        <v>2.2837587441750774e-02</v>
+      </c>
+      <c r="F23" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G23" s="1">
-        <v>1.0635547418921063</v>
+      <c r="G23" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H23" s="5">
+        <v>2.1997138393839981e-02</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E24" s="3">
-        <v>2.2141646921020147e-02</v>
-      </c>
-      <c r="F24" s="4">
+        <v>1.5797567148739283e-02</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G24" s="4">
         <v>2.e-02</v>
       </c>
-      <c r="G24" s="1">
-        <v>2.2994449754967587</v>
+      <c r="H24" s="5">
+        <v>2.0663268933527153e-02</v>
       </c>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E25" s="3">
-        <v>2.1699035796102186e-02</v>
-      </c>
-      <c r="F25" s="4">
+        <v>2.2741899265868077e-02</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1.e-02</v>
+      </c>
+      <c r="G25" s="4">
         <v>2.e-02</v>
       </c>
-      <c r="G25" s="1">
-        <v>0.57409306982766151</v>
+      <c r="H25" s="5">
+        <v>2.050731937345103e-02</v>
       </c>
     </row>
     <row r="26" ht="14.25">
       <c r="A26" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E26" s="3">
-        <v>2.0270896772761948e-02</v>
-      </c>
-      <c r="F26" s="4">
+        <v>2.2141646921020147e-02</v>
+      </c>
+      <c r="F26" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G26" s="1">
-        <v>2.3424123337571312</v>
+      <c r="G26" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H26" s="5">
+        <v>2.0249340375701547e-02</v>
       </c>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="E27" s="3">
-        <v>2.0108078785986434e-02</v>
-      </c>
-      <c r="F27" s="4">
+        <v>2.2977675579801321e-02</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="G27" s="4">
         <v>2.e-02</v>
       </c>
-      <c r="G27" s="1">
-        <v>0.1319383911049645</v>
+      <c r="H27" s="5">
+        <v>1.9901151620644191e-02</v>
       </c>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="E28" s="3">
-        <v>1.9233893028455604e-02</v>
-      </c>
-      <c r="F28" s="4">
+        <v>2.3529974058399253e-02</v>
+      </c>
+      <c r="F28" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G28" s="1">
-        <v>6.8740535872243731</v>
+      <c r="G28" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H28" s="5">
+        <v>1.9807013521645291e-02</v>
       </c>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E29" s="3">
-        <v>1.5924694893597595e-02</v>
-      </c>
-      <c r="F29" s="4">
+        <v>2.4403565241898753e-02</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G29" s="4">
         <v>2.e-02</v>
       </c>
-      <c r="G29" s="1">
-        <v>2.5593149997167481</v>
+      <c r="H29" s="5">
+        <v>1.9797141836327435e-02</v>
       </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="E30" s="3">
-        <v>1.2198249976658535e-02</v>
-      </c>
-      <c r="F30" s="4">
+        <v>2.7878086561949296e-02</v>
+      </c>
+      <c r="F30" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G30" s="1">
-        <v>0.37641799770710743</v>
+      <c r="G30" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H30" s="5">
+        <v>1.9170539093880154e-02</v>
       </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="E31" s="3">
-        <v>1.1098145244875833e-02</v>
-      </c>
-      <c r="F31" s="4">
+        <v>1.9233893028455604e-02</v>
+      </c>
+      <c r="F31" s="3">
         <v>2.e-02</v>
       </c>
-      <c r="G31" s="1">
-        <v>1.2999238318426021</v>
+      <c r="G31" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H31" s="5">
+        <v>1.8094071797290112e-02</v>
       </c>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E32" s="3">
-        <v>8.6036655312242694e-03</v>
-      </c>
-      <c r="F32" s="4">
+        <v>1.7551131962024825e-02</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G32" s="4">
         <v>2.e-02</v>
       </c>
-      <c r="G32" s="1">
-        <v>0.14067084935828603</v>
+      <c r="H32" s="5">
+        <v>1.7824338577568374e-02</v>
       </c>
     </row>
     <row r="33" ht="14.25">
       <c r="A33" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E33" s="3">
-        <v>2.4403565241898753e-02</v>
-      </c>
-      <c r="F33" s="4">
+        <v>1.8473428879071552e-02</v>
+      </c>
+      <c r="F33" s="3">
         <v>1.4999999999999999e-02</v>
       </c>
-      <c r="G33" s="1">
-        <v>0.87275975506490955</v>
+      <c r="G33" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H33" s="5">
+        <v>1.7168756771723921e-02</v>
       </c>
     </row>
     <row r="34" ht="14.25">
       <c r="A34" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="E34" s="3">
-        <v>1.8473428879071552e-02</v>
-      </c>
-      <c r="F34" s="4">
-        <v>1.4999999999999999e-02</v>
-      </c>
-      <c r="G34" s="1">
-        <v>1.0896613084486326</v>
+        <v>2.0108078785986434e-02</v>
+      </c>
+      <c r="F34" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G34" s="4">
+        <v>2.e-02</v>
+      </c>
+      <c r="H34" s="5">
+        <v>1.4329526471500953e-02</v>
       </c>
     </row>
     <row r="35" ht="14.25">
       <c r="A35" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E35" s="3">
-        <v>1.782528600939615e-02</v>
-      </c>
-      <c r="F35" s="4">
+        <v>2.2384977711044654e-02</v>
+      </c>
+      <c r="F35" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G35" s="4">
         <v>1.4999999999999999e-02</v>
       </c>
-      <c r="G35" s="1">
-        <v>8.6427207419562393</v>
+      <c r="H35" s="5">
+        <v>2.6458242311494837e-02</v>
       </c>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E36" s="3">
-        <v>1.7551131962024825e-02</v>
-      </c>
-      <c r="F36" s="4">
+        <v>1.9519654650856855e-02</v>
+      </c>
+      <c r="F36" s="3">
+        <v>1.e-02</v>
+      </c>
+      <c r="G36" s="4">
         <v>1.4999999999999999e-02</v>
       </c>
-      <c r="G36" s="1">
-        <v>0.55108594916058629</v>
+      <c r="H36" s="5">
+        <v>2.4549201735994886e-02</v>
       </c>
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="E37" s="3">
-        <v>1.5797567148739283e-02</v>
-      </c>
-      <c r="F37" s="4">
+        <v>2.9175859286267512e-02</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G37" s="4">
         <v>1.4999999999999999e-02</v>
       </c>
-      <c r="G37" s="1">
-        <v>2.1754210318774421</v>
+      <c r="H37" s="5">
+        <v>2.1235989867584643e-02</v>
       </c>
     </row>
     <row r="38" ht="14.25">
       <c r="A38" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E38" s="3">
-        <v>1.4464766120519525e-02</v>
-      </c>
-      <c r="F38" s="4">
+        <v>1.782528600939615e-02</v>
+      </c>
+      <c r="F38" s="3">
         <v>1.4999999999999999e-02</v>
       </c>
-      <c r="G38" s="1">
-        <v>0.60859565552331674</v>
+      <c r="G38" s="4">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="H38" s="5">
+        <v>2.0795474461103632e-02</v>
       </c>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="E39" s="3">
         <v>1.3998904335095513e-02</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="3">
         <v>1.4999999999999999e-02</v>
       </c>
-      <c r="G39" s="1">
-        <v>1.1046817068353905</v>
+      <c r="G39" s="4">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="H39" s="5">
+        <v>1.702275695273987e-02</v>
       </c>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="E40" s="3">
-        <v>1.3266001122805918e-02</v>
-      </c>
-      <c r="F40" s="4">
+        <v>1.2198249976658535e-02</v>
+      </c>
+      <c r="F40" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G40" s="4">
         <v>1.4999999999999999e-02</v>
       </c>
-      <c r="G40" s="1">
-        <v>3.7095672019851853</v>
+      <c r="H40" s="5">
+        <v>1.5990350090742338e-02</v>
       </c>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="E41" s="3">
-        <v>2.2741899265868077e-02</v>
-      </c>
-      <c r="F41" s="4">
+        <v>1.6607913200733296e-02</v>
+      </c>
+      <c r="F41" s="3">
         <v>1.e-02</v>
       </c>
-      <c r="G41" s="1">
-        <v>1.9962383200498177</v>
+      <c r="G41" s="4">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="H41" s="5">
+        <v>1.428142619056226e-02</v>
       </c>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="E42" s="3">
-        <v>1.9796194208153834e-02</v>
-      </c>
-      <c r="F42" s="4">
+        <v>6.6293257797714628e-03</v>
+      </c>
+      <c r="F42" s="3">
         <v>1.e-02</v>
       </c>
-      <c r="G42" s="1">
-        <v>0.12710013908497675</v>
+      <c r="G42" s="4">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="H42" s="5">
+        <v>1.1928486963647912e-02</v>
       </c>
     </row>
     <row r="43" ht="14.25">
       <c r="A43" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="E43" s="3">
-        <v>1.9519654650856855e-02</v>
-      </c>
-      <c r="F43" s="4">
-        <v>1.e-02</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0.70567239676096361</v>
+        <v>1.3266001122805918e-02</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G43" s="4">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="H43" s="5">
+        <v>1.0542889211305421e-02</v>
       </c>
     </row>
     <row r="44" ht="14.25">
       <c r="A44" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E44" s="3">
-        <v>1.8712999208829139e-02</v>
-      </c>
-      <c r="F44" s="4">
+        <v>1.9796194208153834e-02</v>
+      </c>
+      <c r="F44" s="3">
         <v>1.e-02</v>
       </c>
-      <c r="G44" s="1">
-        <v>1.5305588941021466</v>
+      <c r="G44" s="4">
+        <v>1.e-02</v>
+      </c>
+      <c r="H44" s="5">
+        <v>2.1298689474776509e-02</v>
       </c>
     </row>
     <row r="45" ht="14.25">
       <c r="A45" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E45" s="3">
-        <v>1.7331331276876891e-02</v>
-      </c>
-      <c r="F45" s="4">
+        <v>1.8712999208829139e-02</v>
+      </c>
+      <c r="F45" s="3">
         <v>1.e-02</v>
       </c>
-      <c r="G45" s="1">
-        <v>0.60311504607451916</v>
+      <c r="G45" s="4">
+        <v>1.e-02</v>
+      </c>
+      <c r="H45" s="5">
+        <v>1.6470667885824689e-02</v>
       </c>
     </row>
     <row r="46" ht="14.25">
       <c r="A46" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E46" s="3">
-        <v>1.6607913200733296e-02</v>
-      </c>
-      <c r="F46" s="4">
+        <v>1.4464766120519525e-02</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G46" s="4">
         <v>1.e-02</v>
       </c>
-      <c r="G46" s="1">
-        <v>0.4380387111092186</v>
+      <c r="H46" s="5">
+        <v>1.4985482296935235e-02</v>
       </c>
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E47" s="3">
-        <v>1.2657258221059748e-02</v>
-      </c>
-      <c r="F47" s="4">
+        <v>1.7331331276876891e-02</v>
+      </c>
+      <c r="F47" s="3">
         <v>1.e-02</v>
       </c>
-      <c r="G47" s="1">
-        <v>5.1655461633308679</v>
+      <c r="G47" s="4">
+        <v>1.e-02</v>
+      </c>
+      <c r="H47" s="5">
+        <v>1.4649795856304019e-02</v>
       </c>
     </row>
     <row r="48" ht="14.25">
@@ -2141,96 +2302,106 @@
         <v>137</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E48" s="3">
-        <v>1.20868276388375e-02</v>
-      </c>
-      <c r="F48" s="4">
+        <v>1.2657258221059748e-02</v>
+      </c>
+      <c r="F48" s="3">
         <v>1.e-02</v>
       </c>
-      <c r="G48" s="1">
-        <v>1.1700646584840029e-02</v>
+      <c r="G48" s="4">
+        <v>1.e-02</v>
+      </c>
+      <c r="H48" s="5">
+        <v>1.2302146512128026e-02</v>
       </c>
     </row>
     <row r="49" ht="14.25">
       <c r="A49" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="E49" s="3">
-        <v>6.6293257797714628e-03</v>
-      </c>
-      <c r="F49" s="4">
+        <v>8.6036655312242694e-03</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G49" s="4">
         <v>1.e-02</v>
       </c>
-      <c r="G49" s="1">
-        <v>0.34649585874593342</v>
+      <c r="H49" s="5">
+        <v>1.1879035525123142e-02</v>
       </c>
     </row>
     <row r="50" ht="14.25">
       <c r="A50" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="E50" s="3">
-        <v>1.0450184256466147e-03</v>
-      </c>
-      <c r="F50" s="4">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3">
         <v>1.e-02</v>
       </c>
-      <c r="G50" s="1">
-        <v>7.2065708121402894e-02</v>
+      <c r="G50" s="4">
+        <v>5.0000000000000001e-03</v>
+      </c>
+      <c r="H50" s="5">
+        <v>1.0036131633024442e-02</v>
       </c>
     </row>
     <row r="51" ht="14.25">
       <c r="A51" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="E51" s="3">
-        <v>0</v>
-      </c>
-      <c r="F51" s="4">
+        <v>1.0450184256466147e-03</v>
+      </c>
+      <c r="F51" s="3">
         <v>1.e-02</v>
       </c>
-      <c r="G51" s="1">
-        <v>0.19562913777927843</v>
-      </c>
-    </row>
-    <row r="52" ht="14.25">
-      <c r="F52" s="5"/>
-    </row>
+      <c r="G51" s="4">
+        <v>5.0000000000000001e-03</v>
+      </c>
+      <c r="H51" s="5">
+        <v>6.4675684276815498e-03</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25"/>
   </sheetData>
-  <sortState ref="A2:G51" columnSort="0">
-    <sortCondition sortBy="value" descending="0" ref="F2:F51"/>
+  <sortState ref="A2:H51" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="G2:G51"/>
   </sortState>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -2243,6 +2414,432 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
+    <col bestFit="1" min="2" max="2" width="19.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2">
+        <v>2.0249340375701547e-02</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3">
+        <v>2.8352089725409115e-02</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4">
+        <v>2.2524399757407488e-02</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5">
+        <v>1.0542889211305421e-02</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <v>2.3089961559775309e-02</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7">
+        <v>2.6458242311494837e-02</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8">
+        <v>2.0829207947211357e-02</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9">
+        <v>2.050731937345103e-02</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10">
+        <v>2.1235989867584643e-02</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>1.7824338577568374e-02</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12">
+        <v>2.8788334737737748e-02</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13">
+        <v>1.5990350090742338e-02</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14">
+        <v>1.9170539093880154e-02</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15">
+        <v>2.245773102572042e-02</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16">
+        <v>1.2302146512128026e-02</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17">
+        <v>1.4985482296935235e-02</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18">
+        <v>1.9797141836327435e-02</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19">
+        <v>6.4675684276815498e-03</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>3.4702113934566049e-02</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>2.1015659879092135e-02</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>8.0822989818199395e-03</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23">
+        <v>1.1928486963647912e-02</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24">
+        <v>2.2364703842172446e-02</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25">
+        <v>1.428142619056226e-02</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26">
+        <v>2.374164343461406e-02</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27">
+        <v>2.0663268933527153e-02</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28">
+        <v>2.9830450923956489e-02</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29">
+        <v>2.1298689474776509e-02</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30">
+        <v>2.4499003248388124e-02</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31">
+        <v>1.1879035525123142e-02</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32">
+        <v>2.4549201735994886e-02</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33">
+        <v>2.0795474461103632e-02</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34">
+        <v>3.206075137216953e-02</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35">
+        <v>1.9807013521645291e-02</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36">
+        <v>2.2136447362695606e-02</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37">
+        <v>2.1997138393839981e-02</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38">
+        <v>1.928301982771527e-02</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39">
+        <v>1.0036131633024442e-02</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40">
+        <v>1.702275695273987e-02</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41">
+        <v>2.5045730085698558e-02</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42">
+        <v>2.7134502405334247e-02</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43">
+        <v>1.7168756771723921e-02</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44">
+        <v>2.5833436819371197e-02</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45">
+        <v>1.6470667885824689e-02</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46">
+        <v>1.8094071797290112e-02</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47">
+        <v>1.4649795856304019e-02</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48">
+        <v>1.4329526471500953e-02</v>
+      </c>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49">
+        <v>2.2106707876867186e-02</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50">
+        <v>1.9901151620644191e-02</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51">
+        <v>1.5717863088204321e-02</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:B51" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="A2:A51"/>
+  </sortState>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="11.140625"/>
     <col bestFit="1" min="2" max="2" width="28.140625"/>
   </cols>
@@ -2255,15 +2852,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C2" s="7">
         <v>5.0000000000000003e-02</v>
@@ -2271,10 +2868,10 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C3" s="7">
         <v>4.0000000000000001e-02</v>
@@ -2282,10 +2879,10 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="8" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C4" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2293,10 +2890,10 @@
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="8" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="C5" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2304,10 +2901,10 @@
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2315,10 +2912,10 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="8" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C7" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2326,10 +2923,10 @@
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="C8" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2337,10 +2934,10 @@
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2348,10 +2945,10 @@
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="8" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="C10" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2359,10 +2956,10 @@
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="8" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C11" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2370,10 +2967,10 @@
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="8" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C12" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2381,10 +2978,10 @@
     </row>
     <row r="13" ht="14.25">
       <c r="A13" s="8" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C13" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2392,10 +2989,10 @@
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="8" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="C14" s="9">
         <v>2.9999999999999999e-02</v>
@@ -2403,10 +3000,10 @@
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C15" s="7">
         <v>2.e-02</v>
@@ -2414,10 +3011,10 @@
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C16" s="7">
         <v>2.e-02</v>
@@ -2425,10 +3022,10 @@
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="1" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="C17" s="7">
         <v>2.e-02</v>
@@ -2436,10 +3033,10 @@
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="C18" s="7">
         <v>2.e-02</v>
@@ -2447,10 +3044,10 @@
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="1" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C19" s="7">
         <v>2.e-02</v>
@@ -2458,10 +3055,10 @@
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C20" s="7">
         <v>2.e-02</v>
@@ -2469,10 +3066,10 @@
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C21" s="7">
         <v>2.e-02</v>
@@ -2480,10 +3077,10 @@
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C22" s="7">
         <v>2.e-02</v>
@@ -2491,10 +3088,10 @@
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C23" s="7">
         <v>2.e-02</v>
@@ -2502,10 +3099,10 @@
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="1" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="C24" s="7">
         <v>2.e-02</v>
@@ -2513,10 +3110,10 @@
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C25" s="7">
         <v>2.e-02</v>
@@ -2524,10 +3121,10 @@
     </row>
     <row r="26" ht="14.25">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C26" s="7">
         <v>2.e-02</v>
@@ -2535,10 +3132,10 @@
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C27" s="7">
         <v>2.e-02</v>
@@ -2546,10 +3143,10 @@
     </row>
     <row r="28" ht="14.25">
       <c r="A28" s="1" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C28" s="7">
         <v>2.e-02</v>
@@ -2557,10 +3154,10 @@
     </row>
     <row r="29" ht="14.25">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C29" s="7">
         <v>2.e-02</v>
@@ -2568,10 +3165,10 @@
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="1" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C30" s="7">
         <v>2.e-02</v>
@@ -2579,10 +3176,10 @@
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="1" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="C31" s="7">
         <v>2.e-02</v>
@@ -2590,10 +3187,10 @@
     </row>
     <row r="32" ht="14.25">
       <c r="A32" s="1" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="C32" s="7">
         <v>2.e-02</v>
@@ -2601,10 +3198,10 @@
     </row>
     <row r="33" ht="14.25">
       <c r="A33" s="1" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C33" s="7">
         <v>2.e-02</v>
@@ -2612,10 +3209,10 @@
     </row>
     <row r="34" ht="14.25">
       <c r="A34" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C34" s="7">
         <v>1.e-02</v>
@@ -2623,10 +3220,10 @@
     </row>
     <row r="35" ht="14.25">
       <c r="A35" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C35" s="7">
         <v>1.e-02</v>
@@ -2645,10 +3242,10 @@
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C37" s="7">
         <v>1.e-02</v>
@@ -2656,10 +3253,10 @@
     </row>
     <row r="38" ht="14.25">
       <c r="A38" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="C38" s="7">
         <v>1.e-02</v>
@@ -2667,10 +3264,10 @@
     </row>
     <row r="39" ht="14.25">
       <c r="A39" s="1" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C39" s="7">
         <v>1.e-02</v>
@@ -2678,10 +3275,10 @@
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C40" s="7">
         <v>1.e-02</v>
@@ -2689,10 +3286,10 @@
     </row>
     <row r="41" ht="14.25">
       <c r="A41" s="1" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C41" s="7">
         <v>1.e-02</v>
@@ -2700,10 +3297,10 @@
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C42" s="7">
         <v>1.e-02</v>
@@ -2711,10 +3308,10 @@
     </row>
     <row r="43" ht="14.25">
       <c r="A43" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C43" s="7">
         <v>1.e-02</v>
@@ -2722,10 +3319,10 @@
     </row>
     <row r="44" ht="14.25">
       <c r="A44" s="1" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C44" s="7">
         <v>1.e-02</v>
@@ -2733,10 +3330,10 @@
     </row>
     <row r="45" ht="14.25">
       <c r="A45" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C45" s="7">
         <v>1.e-02</v>
@@ -2744,10 +3341,10 @@
     </row>
     <row r="46" ht="14.25">
       <c r="A46" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="C46" s="7">
         <v>1.e-02</v>
@@ -2755,10 +3352,10 @@
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C47" s="7">
         <v>1.e-02</v>
@@ -2766,10 +3363,10 @@
     </row>
     <row r="48" ht="14.25">
       <c r="A48" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C48" s="7">
         <v>1.e-02</v>
@@ -2777,10 +3374,10 @@
     </row>
     <row r="49" ht="14.25">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B49" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C49" s="10">
         <v>1.e-02</v>
@@ -2788,10 +3385,10 @@
     </row>
     <row r="50" ht="14.25">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C50" s="10">
         <v>0</v>
@@ -2799,10 +3396,10 @@
     </row>
     <row r="51" ht="14.25">
       <c r="A51" t="s">
-        <v>36</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C51" s="10">
         <v>0</v>
@@ -2821,7 +3418,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" id="{001900C0-003B-4FB2-8F8A-001800C700C9}">
+          <x14:cfRule type="containsText" priority="1" id="{00F30013-00A8-4DA3-937D-002A0003001D}">
             <xm:f>NOT(ISERROR(SEARCH("$J$5",I2)))</xm:f>
             <xm:f>$J$5</xm:f>
             <x14:dxf>
@@ -2844,9 +3441,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="2" max="2" width="28.140625"/>
     <col bestFit="1" min="3" max="3" width="21.7109375"/>
@@ -2877,39 +3474,39 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>6</v>
+        <v>148</v>
       </c>
       <c r="G1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3">
         <v>3.3426578117660671e-02</v>
@@ -2938,16 +3535,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
       </c>
       <c r="E3" s="3">
         <v>3.1424819508328677e-02</v>
@@ -2976,16 +3573,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="3">
         <v>3.0962634061024067e-02</v>
@@ -3014,16 +3611,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <v>3.052356663662641e-02</v>
@@ -3052,16 +3649,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3">
         <v>3.0292282855981574e-02</v>
@@ -3090,16 +3687,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3">
         <v>2.9899510066812067e-02</v>
@@ -3128,16 +3725,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3">
         <v>2.9175859286267512e-02</v>
@@ -3166,16 +3763,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
         <v>2.8815825506352546e-02</v>
@@ -3204,16 +3801,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="E10" s="3">
         <v>2.7878086561949296e-02</v>
@@ -3242,16 +3839,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3">
         <v>2.7534380619805943e-02</v>
@@ -3280,16 +3877,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E12" s="3">
         <v>2.7132928626070054e-02</v>
@@ -3318,16 +3915,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3">
         <v>2.5899480754485733e-02</v>
@@ -3356,16 +3953,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E14" s="3">
         <v>2.4805671292413338e-02</v>
@@ -3394,16 +3991,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E15" s="3">
         <v>2.4403565241898753e-02</v>
@@ -3432,16 +4029,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3">
         <v>2.4002268007459516e-02</v>
@@ -3470,16 +4067,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E17" s="3">
         <v>2.3529974058399253e-02</v>
@@ -3508,16 +4105,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E18" s="3">
         <v>2.339145668227165e-02</v>
@@ -3546,16 +4143,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="E19" s="3">
         <v>2.2977675579801321e-02</v>
@@ -3584,16 +4181,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E20" s="3">
         <v>2.2837587441750774e-02</v>
@@ -3622,16 +4219,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3">
         <v>2.2745125426314856e-02</v>
@@ -3660,16 +4257,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="E22" s="3">
         <v>2.2741899265868077e-02</v>
@@ -3698,16 +4295,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="E23" s="3">
         <v>2.2384977711044654e-02</v>
@@ -3736,16 +4333,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E24" s="3">
         <v>2.2141646921020147e-02</v>
@@ -3774,16 +4371,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="E25" s="3">
         <v>2.1699035796102186e-02</v>
@@ -3812,16 +4409,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="E26" s="3">
         <v>2.0270896772761948e-02</v>
@@ -3850,16 +4447,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E27" s="3">
         <v>2.0108078785986434e-02</v>
@@ -3888,16 +4485,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="E28" s="3">
         <v>1.9796194208153834e-02</v>
@@ -3926,16 +4523,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E29" s="3">
         <v>1.9519654650856855e-02</v>
@@ -3964,16 +4561,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E30" s="3">
         <v>1.9233893028455604e-02</v>
@@ -4002,16 +4599,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
         <v>32</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>33</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>34</v>
-      </c>
-      <c r="D31" t="s">
-        <v>35</v>
       </c>
       <c r="E31" s="3">
         <v>1.8889675597916298e-02</v>
@@ -4040,16 +4637,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E32" s="3">
         <v>1.8712999208829139e-02</v>
@@ -4084,10 +4681,10 @@
         <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D33" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E33" s="3">
         <v>1.8473428879071552e-02</v>
@@ -4116,16 +4713,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E34" s="3">
         <v>1.782528600939615e-02</v>
@@ -4154,16 +4751,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E35" s="3">
         <v>1.7551131962024825e-02</v>
@@ -4192,16 +4789,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E36" s="3">
         <v>1.7331331276876891e-02</v>
@@ -4230,16 +4827,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E37" s="3">
         <v>1.6607913200733296e-02</v>
@@ -4268,16 +4865,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D38" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E38" s="3">
         <v>1.5924694893597595e-02</v>
@@ -4306,16 +4903,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D39" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="E39" s="3">
         <v>1.5797567148739283e-02</v>
@@ -4344,16 +4941,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="E40" s="3">
         <v>1.4464766120519525e-02</v>
@@ -4382,16 +4979,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="E41" s="3">
         <v>1.3998904335095513e-02</v>
@@ -4420,16 +5017,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="E42" s="3">
         <v>1.3266001122805918e-02</v>
@@ -4458,16 +5055,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E43" s="3">
         <v>1.2657258221059748e-02</v>
@@ -4496,16 +5093,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E44" s="3">
         <v>1.2198249976658535e-02</v>
@@ -4534,16 +5131,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="E45" s="3">
         <v>1.20868276388375e-02</v>
@@ -4572,16 +5169,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E46" s="3">
         <v>1.1098145244875833e-02</v>
@@ -4610,16 +5207,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="E47" s="3">
         <v>8.6036655312242694e-03</v>
@@ -4648,16 +5245,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E48" s="3">
         <v>7.2822559543963706e-03</v>
@@ -4686,16 +5283,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D49" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E49" s="3">
         <v>6.6293257797714628e-03</v>
@@ -4724,16 +5321,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B50" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="E50" s="3">
         <v>1.0450184256466147e-03</v>
@@ -4762,16 +5359,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" t="s">
         <v>142</v>
       </c>
-      <c r="B51" t="s">
-        <v>143</v>
-      </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E51" s="3">
         <v>0</v>
@@ -4811,7 +5408,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{004C0067-00BA-47A4-AAD3-00590047001C}">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{00FB001B-0098-4FAC-B240-00AA00910026}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4828,7 +5425,7 @@
           <xm:sqref>G2:G51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{009E0047-0075-4B53-9EB3-005C001B0084}">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{008700F8-0038-43BC-B5E6-0044009B004A}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4845,7 +5442,7 @@
           <xm:sqref>H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{004400C0-00FD-45F3-B233-007900CB004C}">
+          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{0064007F-000F-4375-95B0-00A60011003B}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4862,7 +5459,7 @@
           <xm:sqref>G2:G51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{00D90051-0000-4FD4-9189-005E00AA0095}">
+          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{000500DB-002A-4E56-94F2-0038003700D9}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4879,7 +5476,7 @@
           <xm:sqref>H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" id="{008B000F-005D-4418-B25A-0090009200FB}">
+          <x14:cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" id="{00590076-006B-406C-9CC3-00270037009A}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -4896,7 +5493,7 @@
           <xm:sqref>J2:J51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="lessThan" id="{00120069-0055-4B80-ACF4-00DF002C004B}">
+          <x14:cfRule type="cellIs" priority="7" operator="lessThan" id="{007F00F0-004D-4F0C-8A0D-008A00F700E9}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -4913,7 +5510,7 @@
           <xm:sqref>J2:J51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" id="{001600CF-0075-4413-B998-0061002C0010}">
+          <x14:cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" id="{00CD0050-0074-4EE8-A106-006C00FD00A8}">
             <xm:f>1</xm:f>
             <x14:dxf>
               <font>
@@ -4930,7 +5527,7 @@
           <xm:sqref>K2:K51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{006A00EF-00C3-4D3F-810F-00C300F50023}">
+          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{004C00A3-00DF-44A9-8404-009800230024}">
             <xm:f>1</xm:f>
             <x14:dxf>
               <font>
@@ -4947,7 +5544,7 @@
           <xm:sqref>K2:K51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{00630049-00A8-49AA-9BEF-00FB007400DE}">
+          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{008200BE-0053-4429-A0E3-00F4004F00DF}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -4964,7 +5561,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" id="{00810061-00AD-4EFD-981D-000700F4001B}">
+          <x14:cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" id="{005C005A-00DB-4DC2-AE1A-003C00F1007F}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -4981,7 +5578,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" id="{00A5002C-0065-4E7D-9CE4-00AD00E200FD}">
+          <x14:cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" id="{001900D7-0093-46A1-A575-00E400DA001A}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -4998,7 +5595,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{00890047-00F5-467A-8F1B-00480097005C}">
+          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{00AB001F-008C-4AEA-A106-00D5009A0077}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -5020,7 +5617,1974 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" width="11.140625"/>
+    <col bestFit="1" min="2" max="2" width="28.140625"/>
+    <col bestFit="1" min="3" max="3" width="21.7109375"/>
+    <col bestFit="1" min="4" max="4" width="33.8515625"/>
+    <col bestFit="1" min="5" max="5" width="11.28125"/>
+    <col min="6" max="6" width="11.28125"/>
+    <col bestFit="1" min="7" max="7" width="17.57421875"/>
+    <col bestFit="1" min="9" max="9" width="14.7109375"/>
+    <col bestFit="1" min="11" max="11" width="15.421875"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3.2980211092431065e-02</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1.3640389074372375e-03</v>
+      </c>
+      <c r="H2">
+        <v>-1.5302725060923106e-02</v>
+      </c>
+      <c r="I2">
+        <v>0.5486386454128751</v>
+      </c>
+      <c r="J2">
+        <v>-0.27623668572137361</v>
+      </c>
+      <c r="K2">
+        <v>4.8008923155568732</v>
+      </c>
+      <c r="L2">
+        <v>0.21592913082140042</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2.3065267907863542e-02</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.0913392335537748e-02</v>
+      </c>
+      <c r="H3">
+        <v>2.3056680226964429e-02</v>
+      </c>
+      <c r="I3">
+        <v>-0.34200850623140294</v>
+      </c>
+      <c r="J3">
+        <v>-0.2881410272726308</v>
+      </c>
+      <c r="K3">
+        <v>3.9405361646039645</v>
+      </c>
+      <c r="L3">
+        <v>0.19398433823778416</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.7112096763365787e-02</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G4" s="3">
+        <v>5.540078513510306e-04</v>
+      </c>
+      <c r="H4">
+        <v>-0.12998926948448683</v>
+      </c>
+      <c r="I4">
+        <v>0.63770336057730292</v>
+      </c>
+      <c r="J4">
+        <v>-0.42890575483071369</v>
+      </c>
+      <c r="K4">
+        <v>2.0699389217255577</v>
+      </c>
+      <c r="L4">
+        <v>0.14854365028646832</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.5125366783840714e-02</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4.1661310405320982e-04</v>
+      </c>
+      <c r="H5">
+        <v>0.86364157355183202</v>
+      </c>
+      <c r="I5">
+        <v>0.69707983735358792</v>
+      </c>
+      <c r="J5">
+        <v>-0.30721628204929197</v>
+      </c>
+      <c r="K5">
+        <v>-5.225709684937057e-02</v>
+      </c>
+      <c r="L5">
+        <v>4.9285915460568486e-02</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4.0381665566972993e-02</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4.0000000000000001e-02</v>
+      </c>
+      <c r="G6" s="3">
+        <v>4.1265430695822721e-03</v>
+      </c>
+      <c r="H6">
+        <v>0.90194256063004807</v>
+      </c>
+      <c r="I6">
+        <v>0.5486386454128751</v>
+      </c>
+      <c r="J6">
+        <v>-0.22457006329409124</v>
+      </c>
+      <c r="K6">
+        <v>4.6303050360053115</v>
+      </c>
+      <c r="L6">
+        <v>0.22772146043834285</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.7185950226781169e-02</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1.8810376766352607e-03</v>
+      </c>
+      <c r="H7">
+        <v>8.9747013807697451e-02</v>
+      </c>
+      <c r="I7">
+        <v>-7.4814360738119354e-02</v>
+      </c>
+      <c r="J7">
+        <v>-0.34362891574072563</v>
+      </c>
+      <c r="K7">
+        <v>2.7782405394473306</v>
+      </c>
+      <c r="L7">
+        <v>0.18301773819495359</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.516751532459971e-02</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.5000000000000001e-02</v>
+      </c>
+      <c r="G8" s="3">
+        <v>6.2407448628170577e-03</v>
+      </c>
+      <c r="H8">
+        <v>1.7384694582808835e-02</v>
+      </c>
+      <c r="I8">
+        <v>0.96427398284687149</v>
+      </c>
+      <c r="J8">
+        <v>-0.28493469426102291</v>
+      </c>
+      <c r="K8">
+        <v>2.8835132881786478</v>
+      </c>
+      <c r="L8">
+        <v>0.14687417167063921</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.2643734901931362e-03</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.37349113612578944</v>
+      </c>
+      <c r="H9">
+        <v>9.9141546487955381e-02</v>
+      </c>
+      <c r="I9">
+        <v>-1.6482909953096772</v>
+      </c>
+      <c r="J9">
+        <v>-0.70283102843668444</v>
+      </c>
+      <c r="K9">
+        <v>3.3866360213198763</v>
+      </c>
+      <c r="L9">
+        <v>0.44839824000302975</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.8351501260092357e-02</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4.8079998779469429e-03</v>
+      </c>
+      <c r="H10">
+        <v>0.15171742428498802</v>
+      </c>
+      <c r="I10">
+        <v>1.7658564193267217</v>
+      </c>
+      <c r="J10">
+        <v>-0.6080914493335785</v>
+      </c>
+      <c r="K10">
+        <v>0.675627551261616</v>
+      </c>
+      <c r="L10">
+        <v>9.7108348756415053e-02</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.196489175314608e-02</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G11" s="3">
+        <v>8.8780043637082685e-03</v>
+      </c>
+      <c r="H11">
+        <v>1.1074893953383549</v>
+      </c>
+      <c r="I11">
+        <v>0.78614455251801574</v>
+      </c>
+      <c r="J11">
+        <v>-0.60110929570560545</v>
+      </c>
+      <c r="K11">
+        <v>1.4576490892989178</v>
+      </c>
+      <c r="L11">
+        <v>0.13771371865844007</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.1034030942693117e-02</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5.5927783912030947e-03</v>
+      </c>
+      <c r="H12">
+        <v>0.83346105611496446</v>
+      </c>
+      <c r="I12">
+        <v>-0.75764384366539905</v>
+      </c>
+      <c r="J12">
+        <v>-0.43099803566268258</v>
+      </c>
+      <c r="K12">
+        <v>3.4781988672988082</v>
+      </c>
+      <c r="L12">
+        <v>0.30332993368299555</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.9691696764384856e-02</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G13" s="3">
+        <v>7.7597021916956188e-05</v>
+      </c>
+      <c r="H13">
+        <v>1.7082081202349105e-02</v>
+      </c>
+      <c r="I13">
+        <v>0.72676807574173052</v>
+      </c>
+      <c r="J13">
+        <v>-0.45786125829624336</v>
+      </c>
+      <c r="K13">
+        <v>2.5140124848546761</v>
+      </c>
+      <c r="L13">
+        <v>0.16960327128551667</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5.6934558426866471e-03</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5.0000000000000001e-03</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1.263698690857679e-02</v>
+      </c>
+      <c r="H14">
+        <v>4.2695405698351716e-02</v>
+      </c>
+      <c r="I14">
+        <v>-0.69826736688911384</v>
+      </c>
+      <c r="J14">
+        <v>-0.5428524202954661</v>
+      </c>
+      <c r="K14">
+        <v>1.9170268255151606</v>
+      </c>
+      <c r="L14">
+        <v>0.16936840922693386</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2.1612848078154535e-02</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.0936735430405566e-03</v>
+      </c>
+      <c r="H15">
+        <v>4.7831918545374282e-02</v>
+      </c>
+      <c r="I15">
+        <v>4.3938592814450818e-02</v>
+      </c>
+      <c r="J15">
+        <v>-0.3418479812681211</v>
+      </c>
+      <c r="K15">
+        <v>3.2345980730724655</v>
+      </c>
+      <c r="L15">
+        <v>0.23460448597489014</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.5623604119377809e-02</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G16" s="3">
+        <v>8.3631998594653201e-03</v>
+      </c>
+      <c r="H16">
+        <v>0.54759335163722445</v>
+      </c>
+      <c r="I16">
+        <v>-0.31232026784326034</v>
+      </c>
+      <c r="J16">
+        <v>-0.43829218965529659</v>
+      </c>
+      <c r="K16">
+        <v>2.1130897865227354</v>
+      </c>
+      <c r="L16">
+        <v>0.21522597735274096</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3.1347650966415792e-02</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.5000000000000001e-02</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1.7480020116423995e-03</v>
+      </c>
+      <c r="H17">
+        <v>-1.8222651440436659e-02</v>
+      </c>
+      <c r="I17">
+        <v>-0.3716967446195456</v>
+      </c>
+      <c r="J17">
+        <v>-0.31398778778619041</v>
+      </c>
+      <c r="K17">
+        <v>5.852552405319571</v>
+      </c>
+      <c r="L17">
+        <v>0.35915244488460263</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.5035036820334224e-02</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.e-02</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.12663453526670987</v>
+      </c>
+      <c r="H18">
+        <v>-0.68088734627452019</v>
+      </c>
+      <c r="I18">
+        <v>-2.0342380943555312</v>
+      </c>
+      <c r="J18">
+        <v>-0.60268338628534668</v>
+      </c>
+      <c r="K18">
+        <v>6.5498015231649918</v>
+      </c>
+      <c r="L18">
+        <v>0.69765361656431746</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2.8580424264704501e-02</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1.4261161215505789e-03</v>
+      </c>
+      <c r="H19">
+        <v>0.46870808041592471</v>
+      </c>
+      <c r="I19">
+        <v>0.96427398284687149</v>
+      </c>
+      <c r="J19">
+        <v>-0.40732902898648671</v>
+      </c>
+      <c r="K19">
+        <v>3.0937771668461682</v>
+      </c>
+      <c r="L19">
+        <v>0.20129883095328727</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2.8358472898339484e-03</v>
+      </c>
+      <c r="F20" s="3">
+        <v>5.0000000000000001e-03</v>
+      </c>
+      <c r="G20" s="3">
+        <v>8.2783771196874769e-03</v>
+      </c>
+      <c r="H20">
+        <v>1.4434399944520355</v>
+      </c>
+      <c r="I20">
+        <v>-0.16387907590254722</v>
+      </c>
+      <c r="J20">
+        <v>-0.87921200942384936</v>
+      </c>
+      <c r="K20">
+        <v>1.2787200152493377e-03</v>
+      </c>
+      <c r="L20">
+        <v>3.2071752498464612e-02</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1.3359628471997327e-02</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.e-02</v>
+      </c>
+      <c r="G21" s="3">
+        <v>4.6903482696869928e-03</v>
+      </c>
+      <c r="H21">
+        <v>0.97835900363683104</v>
+      </c>
+      <c r="I21">
+        <v>-0.40138498300768821</v>
+      </c>
+      <c r="J21">
+        <v>-0.42832158882024751</v>
+      </c>
+      <c r="K21">
+        <v>1.3667679363026799</v>
+      </c>
+      <c r="L21">
+        <v>0.12122593990942265</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3.2448787056903745e-02</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2.2089351352613485e-03</v>
+      </c>
+      <c r="H22">
+        <v>2.4721441825999405e-02</v>
+      </c>
+      <c r="I22">
+        <v>1.9439858496555771</v>
+      </c>
+      <c r="J22">
+        <v>-0.2148053352787529</v>
+      </c>
+      <c r="K22">
+        <v>2.5314200310848731</v>
+      </c>
+      <c r="L22">
+        <v>0.12843602265199427</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3.1078663771106518e-02</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3.5000000000000003e-02</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2.0750307308092446e-03</v>
+      </c>
+      <c r="H23">
+        <v>1.1967010979526544</v>
+      </c>
+      <c r="I23">
+        <v>2.0627388032081475</v>
+      </c>
+      <c r="J23">
+        <v>-0.72684348978391478</v>
+      </c>
+      <c r="K23">
+        <v>2.4029632505349041</v>
+      </c>
+      <c r="L23">
+        <v>0.30423846863293269</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4.0313637453391955e-02</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4.0000000000000001e-02</v>
+      </c>
+      <c r="G24" s="3">
+        <v>5.6252724636770828e-02</v>
+      </c>
+      <c r="H24">
+        <v>0.6980900441771376</v>
+      </c>
+      <c r="I24">
+        <v>-0.60920265172468657</v>
+      </c>
+      <c r="J24">
+        <v>-0.28151086777143086</v>
+      </c>
+      <c r="K24">
+        <v>7.0706159968729194</v>
+      </c>
+      <c r="L24">
+        <v>0.31579206607615307</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1.4947812995714384e-02</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G25" s="3">
+        <v>4.1330276331170137e-03</v>
+      </c>
+      <c r="H25">
+        <v>0.86662174054212093</v>
+      </c>
+      <c r="I25">
+        <v>-1.5889145185333919</v>
+      </c>
+      <c r="J25">
+        <v>-0.65395237079532098</v>
+      </c>
+      <c r="K25">
+        <v>3.9379868397198239</v>
+      </c>
+      <c r="L25">
+        <v>0.4215721826050729</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4.3723700398078769e-02</v>
+      </c>
+      <c r="F26" s="3">
+        <v>4.0000000000000001e-02</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1.5962393614412332e-03</v>
+      </c>
+      <c r="H26">
+        <v>-0.10420818421554218</v>
+      </c>
+      <c r="I26">
+        <v>0.84552102929430106</v>
+      </c>
+      <c r="J26">
+        <v>-0.30024926048830658</v>
+      </c>
+      <c r="K26">
+        <v>6.5517403345372323</v>
+      </c>
+      <c r="L26">
+        <v>0.32693683275449237</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3.0800114740260325e-02</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2.9999999999999999e-02</v>
+      </c>
+      <c r="G27" s="3">
+        <v>3.0935786452068533e-03</v>
+      </c>
+      <c r="H27">
+        <v>-0.10890754445658185</v>
+      </c>
+      <c r="I27">
+        <v>-4.5126122349977052e-02</v>
+      </c>
+      <c r="J27">
+        <v>-0.27923650848606263</v>
+      </c>
+      <c r="K27">
+        <v>5.1745903007120999</v>
+      </c>
+      <c r="L27">
+        <v>0.23638433986729579</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1.866780880211432e-02</v>
+      </c>
+      <c r="F28" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G28" s="3">
+        <v>4.9479323290228866e-03</v>
+      </c>
+      <c r="H28">
+        <v>0.69000762971109086</v>
+      </c>
+      <c r="I28">
+        <v>-1.4701615649808213</v>
+      </c>
+      <c r="J28">
+        <v>-0.47959808930094716</v>
+      </c>
+      <c r="K28">
+        <v>4.3722419815642652</v>
+      </c>
+      <c r="L28">
+        <v>0.36098411030290634</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1.0053069455554359e-02</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G29" s="3">
+        <v>7.8151758940078128e-03</v>
+      </c>
+      <c r="H29">
+        <v>-2.1731087125775695e-02</v>
+      </c>
+      <c r="I29">
+        <v>-0.60920265172468657</v>
+      </c>
+      <c r="J29">
+        <v>-0.36382443331596537</v>
+      </c>
+      <c r="K29">
+        <v>2.3266436797532895</v>
+      </c>
+      <c r="L29">
+        <v>0.16668725578273769</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2.3656316327064039e-02</v>
+      </c>
+      <c r="F30" s="3">
+        <v>2.3e-02</v>
+      </c>
+      <c r="G30" s="3">
+        <v>7.6635741127772748e-03</v>
+      </c>
+      <c r="H30">
+        <v>3.7028286370345304e-02</v>
+      </c>
+      <c r="I30">
+        <v>0.9939622212350141</v>
+      </c>
+      <c r="J30">
+        <v>-0.19551174544928396</v>
+      </c>
+      <c r="K30">
+        <v>2.0696626738823305</v>
+      </c>
+      <c r="L30">
+        <v>0.11701959231221482</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="3">
+        <v>7.8078953359519308e-03</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1.e-02</v>
+      </c>
+      <c r="G31" s="3">
+        <v>2.1001060789390328e-03</v>
+      </c>
+      <c r="H31">
+        <v>0.72508013893917711</v>
+      </c>
+      <c r="I31">
+        <v>-1.9451733791911034</v>
+      </c>
+      <c r="J31">
+        <v>-0.65287567378900313</v>
+      </c>
+      <c r="K31">
+        <v>3.2182060521014964</v>
+      </c>
+      <c r="L31">
+        <v>0.37147986291600188</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1.3530475135421131e-02</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1.e-02</v>
+      </c>
+      <c r="G32" s="3">
+        <v>2.6629680793169774e-03</v>
+      </c>
+      <c r="H32">
+        <v>2.4863394483117016e-02</v>
+      </c>
+      <c r="I32">
+        <v>-0.31232026784326034</v>
+      </c>
+      <c r="J32">
+        <v>-0.3632420742880198</v>
+      </c>
+      <c r="K32">
+        <v>2.4226791458252204</v>
+      </c>
+      <c r="L32">
+        <v>0.14639528112679212</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1.9706989794432826e-02</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G33" s="3">
+        <v>2.504586736761552e-03</v>
+      </c>
+      <c r="H33">
+        <v>7.2028385928674082e-02</v>
+      </c>
+      <c r="I33">
+        <v>1.2314681283401547</v>
+      </c>
+      <c r="J33">
+        <v>-0.50695931477516065</v>
+      </c>
+      <c r="K33">
+        <v>1.5143286656692232</v>
+      </c>
+      <c r="L33">
+        <v>0.12455101919851597</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>155</v>
+      </c>
+      <c r="D34" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2.327816597403403e-02</v>
+      </c>
+      <c r="F34" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1.6522848719471525e-03</v>
+      </c>
+      <c r="H34">
+        <v>-0.11475119020263212</v>
+      </c>
+      <c r="I34">
+        <v>1.5580387506097233</v>
+      </c>
+      <c r="J34">
+        <v>-0.45042698230557598</v>
+      </c>
+      <c r="K34">
+        <v>2.0142646553577066</v>
+      </c>
+      <c r="L34">
+        <v>0.13077833804538708</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1.7371504943138679e-03</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1.0059153134037973e-02</v>
+      </c>
+      <c r="H35">
+        <v>-0.34737725596521374</v>
+      </c>
+      <c r="I35">
+        <v>-0.28263202945511773</v>
+      </c>
+      <c r="J35">
+        <v>-0.60896652296770926</v>
+      </c>
+      <c r="K35">
+        <v>1.1898908085867539</v>
+      </c>
+      <c r="L35">
+        <v>0.12004761378492068</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1.6947215311778032e-02</v>
+      </c>
+      <c r="F36" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G36" s="3">
+        <v>4.9629573174709146e-03</v>
+      </c>
+      <c r="H36">
+        <v>1.1332536323864348</v>
+      </c>
+      <c r="I36">
+        <v>-0.3716967446195456</v>
+      </c>
+      <c r="J36">
+        <v>-0.48245705030217723</v>
+      </c>
+      <c r="K36">
+        <v>1.912961843994627</v>
+      </c>
+      <c r="L36">
+        <v>0.15450202347378661</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="3">
+        <v>6.7689674834389112e-03</v>
+      </c>
+      <c r="F37" s="3">
+        <v>5.0000000000000001e-03</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1.4539395671791524e-03</v>
+      </c>
+      <c r="H37">
+        <v>5.9086106727353309e-02</v>
+      </c>
+      <c r="I37">
+        <v>-0.19356731429068985</v>
+      </c>
+      <c r="J37">
+        <v>-0.36804809599227517</v>
+      </c>
+      <c r="K37">
+        <v>0.95538701311182728</v>
+      </c>
+      <c r="L37">
+        <v>9.403571069893979e-02</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="3">
+        <v>2.5669876319742841e-02</v>
+      </c>
+      <c r="F38" s="3">
+        <v>2.5000000000000001e-02</v>
+      </c>
+      <c r="G38" s="3">
+        <v>3.6347077160037299e-03</v>
+      </c>
+      <c r="H38">
+        <v>5.3146971569699736e-03</v>
+      </c>
+      <c r="I38">
+        <v>-0.49044969817211609</v>
+      </c>
+      <c r="J38">
+        <v>-0.32652448700655601</v>
+      </c>
+      <c r="K38">
+        <v>4.8032365590362076</v>
+      </c>
+      <c r="L38">
+        <v>0.2878454482802868</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>5.0000000000000001e-03</v>
+      </c>
+      <c r="G39" s="3">
+        <v>4.0568611939166051e-03</v>
+      </c>
+      <c r="H39">
+        <v>0.20902190344074839</v>
+      </c>
+      <c r="I39">
+        <v>-1.5437883961834428e-02</v>
+      </c>
+      <c r="J39">
+        <v>-0.67731915843034196</v>
+      </c>
+      <c r="K39">
+        <v>0.9386638732653424</v>
+      </c>
+      <c r="L39">
+        <v>0.13365045182920787</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="3">
+        <v>3.4903903127292697e-02</v>
+      </c>
+      <c r="F40" s="3">
+        <v>3.5000000000000003e-02</v>
+      </c>
+      <c r="G40" s="3">
+        <v>5.0910838703569728e-03</v>
+      </c>
+      <c r="H40">
+        <v>0.79210231666859232</v>
+      </c>
+      <c r="I40">
+        <v>0.42988569186030462</v>
+      </c>
+      <c r="J40">
+        <v>-0.28045147864627529</v>
+      </c>
+      <c r="K40">
+        <v>3.8576107644569309</v>
+      </c>
+      <c r="L40">
+        <v>0.2162192492027466</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>155</v>
+      </c>
+      <c r="D41" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2.2170108023531771e-02</v>
+      </c>
+      <c r="F41" s="3">
+        <v>4.0000000000000001e-02</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.5674421516471454e-03</v>
+      </c>
+      <c r="H41">
+        <v>2.7396485195259824e-02</v>
+      </c>
+      <c r="I41">
+        <v>0.5486386454128751</v>
+      </c>
+      <c r="J41">
+        <v>-0.27972534632078883</v>
+      </c>
+      <c r="K41">
+        <v>2.5857383156734568</v>
+      </c>
+      <c r="L41">
+        <v>0.15127905651289875</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1.204275820288234e-02</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G42" s="3">
+        <v>7.3792606292316979e-04</v>
+      </c>
+      <c r="H42">
+        <v>1.9343746586245228e-02</v>
+      </c>
+      <c r="I42">
+        <v>-0.46076145978397348</v>
+      </c>
+      <c r="J42">
+        <v>-0.45236846312158396</v>
+      </c>
+      <c r="K42">
+        <v>2.4624974560123905</v>
+      </c>
+      <c r="L42">
+        <v>0.21290162510777577</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
+        <v>155</v>
+      </c>
+      <c r="D43" t="s">
+        <v>155</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4.104901444017256e-02</v>
+      </c>
+      <c r="F43" s="3">
+        <v>4.0000000000000001e-02</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0.10691889250256789</v>
+      </c>
+      <c r="H43">
+        <v>0.68080274831344867</v>
+      </c>
+      <c r="I43">
+        <v>2.0330505648200048</v>
+      </c>
+      <c r="J43">
+        <v>-0.25069047188811933</v>
+      </c>
+      <c r="K43">
+        <v>3.0889742889129765</v>
+      </c>
+      <c r="L43">
+        <v>0.17934606042854329</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" t="s">
+        <v>124</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2.8095910154655214e-02</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G44" s="3">
+        <v>4.7314892242853335e-03</v>
+      </c>
+      <c r="H44">
+        <v>0.7147483065141369</v>
+      </c>
+      <c r="I44">
+        <v>-0.9060850356061122</v>
+      </c>
+      <c r="J44">
+        <v>-0.48022425331613849</v>
+      </c>
+      <c r="K44">
+        <v>5.5428955814731644</v>
+      </c>
+      <c r="L44">
+        <v>0.3655980176694531</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" t="s">
+        <v>124</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1.0521185108879184e-02</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1.e-02</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3.8247906870517777e-03</v>
+      </c>
+      <c r="H45">
+        <v>-0.12040319931087734</v>
+      </c>
+      <c r="I45">
+        <v>-1.5889145185333919</v>
+      </c>
+      <c r="J45">
+        <v>-0.47909700857886373</v>
+      </c>
+      <c r="K45">
+        <v>4.2043272455966623</v>
+      </c>
+      <c r="L45">
+        <v>0.34317148738498959</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2.3374000188728025e-02</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2.3e-02</v>
+      </c>
+      <c r="G46" s="3">
+        <v>6.7613891742915405e-02</v>
+      </c>
+      <c r="H46">
+        <v>-9.7069030974282502e-02</v>
+      </c>
+      <c r="I46">
+        <v>-0.69826736688911384</v>
+      </c>
+      <c r="J46">
+        <v>-0.36257034985415182</v>
+      </c>
+      <c r="K46">
+        <v>5.1313084224013146</v>
+      </c>
+      <c r="L46">
+        <v>0.33546755915855075</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" t="s">
+        <v>99</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1.2762914852215508e-02</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G47" s="3">
+        <v>4.8439178021027082e-02</v>
+      </c>
+      <c r="H47">
+        <v>0.1541597382663914</v>
+      </c>
+      <c r="I47">
+        <v>-0.40138498300768821</v>
+      </c>
+      <c r="J47">
+        <v>-0.50335513155795808</v>
+      </c>
+      <c r="K47">
+        <v>2.6218881982410394</v>
+      </c>
+      <c r="L47">
+        <v>0.21779066354933807</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" t="s">
+        <v>116</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1.4175317216634876e-02</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1.4999999999999999e-02</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2.2206224396393814e-02</v>
+      </c>
+      <c r="H48">
+        <v>-3.53827891997026e-02</v>
+      </c>
+      <c r="I48">
+        <v>-0.49044969817211609</v>
+      </c>
+      <c r="J48">
+        <v>-0.36120245074405199</v>
+      </c>
+      <c r="K48">
+        <v>3.0978934418066211</v>
+      </c>
+      <c r="L48">
+        <v>0.19257373706742942</v>
+      </c>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" t="s">
+        <v>60</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4.9786131509862545e-03</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2.5162674612200014e-03</v>
+      </c>
+      <c r="H49">
+        <v>1.5128434171184211e-02</v>
+      </c>
+      <c r="I49">
+        <v>-0.96546151238239741</v>
+      </c>
+      <c r="J49">
+        <v>-0.59591282148344382</v>
+      </c>
+      <c r="K49">
+        <v>2.2460798697596589</v>
+      </c>
+      <c r="L49">
+        <v>0.23535150877630406</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" s="3">
+        <v>2.2001586031867262e-02</v>
+      </c>
+      <c r="F50" s="3">
+        <v>2.e-02</v>
+      </c>
+      <c r="G50" s="3">
+        <v>4.6056042569108807e-03</v>
+      </c>
+      <c r="H50">
+        <v>1.3417185657462924e-02</v>
+      </c>
+      <c r="I50">
+        <v>0.40019745347216196</v>
+      </c>
+      <c r="J50">
+        <v>-0.37331328041666956</v>
+      </c>
+      <c r="K50">
+        <v>3.2174112517583997</v>
+      </c>
+      <c r="L50">
+        <v>0.2071126005361823</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" t="s">
+        <v>155</v>
+      </c>
+      <c r="E51" s="3">
+        <v>2.0374978922983133e-02</v>
+      </c>
+      <c r="F51" s="3">
+        <v>1.e-02</v>
+      </c>
+      <c r="G51" s="3">
+        <v>2.5658293760374325e-02</v>
+      </c>
+      <c r="H51">
+        <v>-0.39797696791727366</v>
+      </c>
+      <c r="I51">
+        <v>0.5189504070247325</v>
+      </c>
+      <c r="J51">
+        <v>-0.49080079531120557</v>
+      </c>
+      <c r="K51">
+        <v>3.3905237163365816</v>
+      </c>
+      <c r="L51">
+        <v>0.25051811205378871</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="F52" s="11"/>
+    </row>
+  </sheetData>
+  <sortState ref="A2:L51" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="B2:B51"/>
+  </sortState>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
+++ b/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
@@ -1064,12 +1064,11 @@
   <cols>
     <col bestFit="1" min="1" max="1" width="11.140625"/>
     <col bestFit="1" min="2" max="2" width="28.140625"/>
-    <col bestFit="1" min="3" max="3" width="21.7109375"/>
-    <col bestFit="1" min="4" max="4" width="33.8515625"/>
-    <col customWidth="1" min="5" max="5" width="8.140625"/>
-    <col bestFit="1" min="6" max="6" width="10.140625"/>
+    <col customWidth="1" hidden="1" min="3" max="4" width="0"/>
+    <col customWidth="1" hidden="1" min="5" max="5" width="8.140625"/>
+    <col customWidth="1" hidden="1" min="6" max="6" width="0"/>
     <col bestFit="1" min="7" max="7" width="14.7109375"/>
-    <col bestFit="1" min="8" max="8" width="11.421875"/>
+    <col customWidth="1" hidden="1" min="8" max="8" width="0"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -3418,7 +3417,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" id="{00F30013-00A8-4DA3-937D-002A0003001D}">
+          <x14:cfRule type="containsText" priority="1" id="{0000001B-0041-429A-9D6E-00AC007E009C}">
             <xm:f>NOT(ISERROR(SEARCH("$J$5",I2)))</xm:f>
             <xm:f>$J$5</xm:f>
             <x14:dxf>
@@ -5408,7 +5407,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{00FB001B-0098-4FAC-B240-00AA00910026}">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{001100EF-00B9-481D-8AEA-00C500DB0049}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5425,7 +5424,7 @@
           <xm:sqref>G2:G51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{008700F8-0038-43BC-B5E6-0044009B004A}">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{003000DB-0059-4520-9FCE-00FC009E0002}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5442,7 +5441,7 @@
           <xm:sqref>H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{0064007F-000F-4375-95B0-00A60011003B}">
+          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{00B300D8-006A-4120-8960-00BF008F00EF}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5459,7 +5458,7 @@
           <xm:sqref>G2:G51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{000500DB-002A-4E56-94F2-0038003700D9}">
+          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{0035009E-00B1-4A9F-9D61-008E003A00D6}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5476,7 +5475,7 @@
           <xm:sqref>H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" id="{00590076-006B-406C-9CC3-00270037009A}">
+          <x14:cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" id="{0056009E-0089-4728-B97E-00C000DD00E3}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -5493,7 +5492,7 @@
           <xm:sqref>J2:J51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="lessThan" id="{007F00F0-004D-4F0C-8A0D-008A00F700E9}">
+          <x14:cfRule type="cellIs" priority="7" operator="lessThan" id="{00F800A9-0012-4AB4-A65B-009700D200D0}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -5510,7 +5509,7 @@
           <xm:sqref>J2:J51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" id="{00CD0050-0074-4EE8-A106-006C00FD00A8}">
+          <x14:cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" id="{0008004A-005C-4276-BF6E-0074009B0015}">
             <xm:f>1</xm:f>
             <x14:dxf>
               <font>
@@ -5527,7 +5526,7 @@
           <xm:sqref>K2:K51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{004C00A3-00DF-44A9-8404-009800230024}">
+          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{008C00C9-0076-4899-B24B-006E00670035}">
             <xm:f>1</xm:f>
             <x14:dxf>
               <font>
@@ -5544,7 +5543,7 @@
           <xm:sqref>K2:K51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{008200BE-0053-4429-A0E3-00F4004F00DF}">
+          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{00B3007C-001B-4E6B-A469-0021008600EC}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -5561,7 +5560,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" id="{005C005A-00DB-4DC2-AE1A-003C00F1007F}">
+          <x14:cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" id="{0040008A-00BB-4F57-A864-00AC007500D1}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -5578,7 +5577,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" id="{001900D7-0093-46A1-A575-00E400DA001A}">
+          <x14:cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" id="{008C0089-00B0-43A9-A493-00FE00B000DB}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -5595,7 +5594,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{00AB001F-008C-4AEA-A106-00D5009A0077}">
+          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{0067006C-00AD-482D-A4E4-001300A200F2}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>

--- a/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
+++ b/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
@@ -6,30 +6,442 @@
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Portfolio_Stocks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="BBPTACShadowWks0001" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Portfolio_Stocks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="BBPTACShadowWks0001" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t>YahooTicker</t>
   </si>
   <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>Company</t>
   </si>
   <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Industry</t>
+    <t>adj_weight_GBP</t>
+  </si>
+  <si>
+    <t>WM</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waste Management</t>
+  </si>
+  <si>
+    <t>CNR.TO</t>
+  </si>
+  <si>
+    <t>Railroads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canadian National Railway</t>
+  </si>
+  <si>
+    <t>AZN.L</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drug Manufacturers—General</t>
+  </si>
+  <si>
+    <t>AstraZeneca</t>
+  </si>
+  <si>
+    <t>NESN.SW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer Defensive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packaged Foods</t>
+  </si>
+  <si>
+    <t>Nestle</t>
+  </si>
+  <si>
+    <t>MC.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer Cyclical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxury Goods</t>
+  </si>
+  <si>
+    <t>LVMH</t>
+  </si>
+  <si>
+    <t>9984.T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telecom Services</t>
+  </si>
+  <si>
+    <t>SoftBank</t>
+  </si>
+  <si>
+    <t>SMT.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investment Trust </t>
+  </si>
+  <si>
+    <t>SMT</t>
+  </si>
+  <si>
+    <t>FAS.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Asian</t>
+  </si>
+  <si>
+    <t>HVPE.L</t>
+  </si>
+  <si>
+    <t>HarbourVest</t>
+  </si>
+  <si>
+    <t>DG.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>VINCI</t>
+  </si>
+  <si>
+    <t>SMSN.IL</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer Electronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Electronics</t>
+  </si>
+  <si>
+    <t>III.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3i Group</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old Dominion Freight Line, Inc.</t>
+  </si>
+  <si>
+    <t>LIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic Materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialty Chemicals</t>
+  </si>
+  <si>
+    <t>Linde</t>
+  </si>
+  <si>
+    <t>ECL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecolab Inc.</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>Albemarle</t>
+  </si>
+  <si>
+    <t>SHW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sherwin-Williams Company</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software - Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Corp</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>CrowdStrike</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software - Application</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>ServiceNow</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>HubSpot</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lam Research Corporation</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials, Inc.</t>
+  </si>
+  <si>
+    <t>RIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Industrial Metals &amp; Mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rio Tinto</t>
+  </si>
+  <si>
+    <t>BHP</t>
+  </si>
+  <si>
+    <t>XOM</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oil &amp; Gas Integrated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exxon Mobil Corporation</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet Retail</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>MELI</t>
+  </si>
+  <si>
+    <t>MercadoLibre</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet Content &amp; Information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alphabet Inc.</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Procter &amp; Gamble Company</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estee Lauder</t>
+  </si>
+  <si>
+    <t>NKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIKE, Inc.</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm &amp; Heavy Construction Machinery</t>
+  </si>
+  <si>
+    <t>Deere</t>
+  </si>
+  <si>
+    <t>JNJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>ABBV</t>
+  </si>
+  <si>
+    <t>Abbvie</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discount Stores</t>
+  </si>
+  <si>
+    <t>Costco</t>
+  </si>
+  <si>
+    <t>TMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnostics &amp; Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermo Fisher</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit Services</t>
+  </si>
+  <si>
+    <t>Visa</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>HON</t>
+  </si>
+  <si>
+    <t>Conglomerates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honeywell International</t>
+  </si>
+  <si>
+    <t>MRNA</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Moderna</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novo Nordisk</t>
+  </si>
+  <si>
+    <t>JPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banks - Diversified</t>
+  </si>
+  <si>
+    <t>JPMorgan</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Toyota</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>NIO</t>
+  </si>
+  <si>
+    <t>Nio</t>
   </si>
   <si>
     <t>weight</t>
@@ -38,421 +450,13 @@
     <t>adj_weight</t>
   </si>
   <si>
-    <t>adj_weight_GBP</t>
-  </si>
-  <si>
     <t>inv_vol_GBP</t>
   </si>
   <si>
-    <t>CNR.TO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canadian National Railway</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Railroads</t>
-  </si>
-  <si>
-    <t>AZN.L</t>
-  </si>
-  <si>
-    <t>AstraZeneca</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drug Manufacturers—General</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corp</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>NESN.SW</t>
-  </si>
-  <si>
-    <t>Nestle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Defensive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packaged Foods</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>Costco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount Stores</t>
-  </si>
-  <si>
-    <t>MC.PA</t>
-  </si>
-  <si>
-    <t>LVMH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Cyclical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxury Goods</t>
-  </si>
-  <si>
-    <t>9984.T</t>
-  </si>
-  <si>
-    <t>SoftBank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telecom Services</t>
-  </si>
-  <si>
-    <t>MRNA</t>
-  </si>
-  <si>
-    <t>Moderna</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>JNJ</t>
-  </si>
-  <si>
-    <t>Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drug Manufacturers - General</t>
-  </si>
-  <si>
-    <t>PG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Procter &amp; Gamble Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>WM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waste Management</t>
-  </si>
-  <si>
-    <t>SMT.L</t>
-  </si>
-  <si>
-    <t>SMT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Investment Trust</t>
   </si>
   <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>Deere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farm &amp; Heavy Construction Machinery</t>
-  </si>
-  <si>
-    <t>FAS.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Asian</t>
-  </si>
-  <si>
-    <t>HVPE.L</t>
-  </si>
-  <si>
-    <t>HarbourVest</t>
-  </si>
-  <si>
     <t xml:space="preserve">Private Equity</t>
-  </si>
-  <si>
-    <t>LIN</t>
-  </si>
-  <si>
-    <t>Linde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic Materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specialty Chemicals</t>
-  </si>
-  <si>
-    <t>TMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thermo Fisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnostics &amp; Research</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Visa</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit Services</t>
-  </si>
-  <si>
-    <t>NVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novo Nordisk</t>
-  </si>
-  <si>
-    <t>ECL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecolab Inc.</t>
-  </si>
-  <si>
-    <t>ABBV</t>
-  </si>
-  <si>
-    <t>Abbvie</t>
-  </si>
-  <si>
-    <t>DG.PA</t>
-  </si>
-  <si>
-    <t>VINCI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>JPM</t>
-  </si>
-  <si>
-    <t>JPMorgan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banks - Diversified</t>
-  </si>
-  <si>
-    <t>SMSN.IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Electronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Electronics</t>
-  </si>
-  <si>
-    <t>XOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exxon Mobil Corporation</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oil &amp; Gas Integrated</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>EL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estee Lauder</t>
-  </si>
-  <si>
-    <t>NKE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIKE, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Footwear &amp; Accessories</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old Dominion Freight Line, Inc.</t>
-  </si>
-  <si>
-    <t>Trucking</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internet Retail</t>
-  </si>
-  <si>
-    <t>RIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rio Tinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Industrial Metals &amp; Mining</t>
-  </si>
-  <si>
-    <t>BHP</t>
-  </si>
-  <si>
-    <t>ALB</t>
-  </si>
-  <si>
-    <t>Albemarle</t>
-  </si>
-  <si>
-    <t>TM</t>
-  </si>
-  <si>
-    <t>Toyota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto Manufacturers</t>
-  </si>
-  <si>
-    <t>HON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honeywell International</t>
-  </si>
-  <si>
-    <t>Conglomerates</t>
-  </si>
-  <si>
-    <t>SHW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sherwin-Williams Company</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alphabet Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internet Content &amp; Information</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software - Application</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lam Research Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>MELI</t>
-  </si>
-  <si>
-    <t>MercadoLibre</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>Tesla</t>
-  </si>
-  <si>
-    <t>III.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3i Group</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>ServiceNow</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials, Inc.</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>NVIDIA</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>HubSpot</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>CrowdStrike</t>
-  </si>
-  <si>
-    <t>NIO</t>
-  </si>
-  <si>
-    <t>Nio</t>
   </si>
   <si>
     <t>asset</t>
@@ -523,18 +527,18 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -545,7 +549,6 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="161" xfId="1" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
       <protection hidden="0" locked="1"/>
@@ -1063,6 +1066,895 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="1" max="1" width="11.140625"/>
+    <col bestFit="1" min="2" max="2" width="21.7109375"/>
+    <col bestFit="1" min="3" max="3" width="33.8515625"/>
+    <col bestFit="1" min="4" max="4" width="28.140625"/>
+    <col bestFit="1" min="5" max="5" width="14.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>2.5000000000000001e-02</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>4.0000000000000001e-02</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>4.0000000000000001e-02</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>2.5000000000000001e-02</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13">
+        <v>1.e-02</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18">
+        <v>1.4999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19">
+        <v>4.0000000000000001e-02</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20">
+        <v>1.4999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21">
+        <v>5.0000000000000001e-03</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22">
+        <v>1.4999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23">
+        <v>1.e-02</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24">
+        <v>1.e-02</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25">
+        <v>1.e-02</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26">
+        <v>1.4999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27">
+        <v>1.e-02</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28">
+        <v>1.e-02</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" t="s">
+        <v>91</v>
+      </c>
+      <c r="E33">
+        <v>1.4999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34">
+        <v>1.4999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35">
+        <v>2.5000000000000001e-02</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38">
+        <v>2.5000000000000001e-02</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" t="s">
+        <v>108</v>
+      </c>
+      <c r="E39">
+        <v>2.5000000000000001e-02</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" t="s">
+        <v>116</v>
+      </c>
+      <c r="E42">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" t="s">
+        <v>120</v>
+      </c>
+      <c r="E43">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" t="s">
+        <v>123</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>124</v>
+      </c>
+      <c r="D45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E45">
+        <v>1.4999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46" t="s">
+        <v>128</v>
+      </c>
+      <c r="E46">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" t="s">
+        <v>130</v>
+      </c>
+      <c r="E47">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" t="s">
+        <v>132</v>
+      </c>
+      <c r="D48" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48">
+        <v>2.e-02</v>
+      </c>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49">
+        <v>1.4999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" t="s">
+        <v>137</v>
+      </c>
+      <c r="B50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50">
+        <v>1.4999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51">
+        <v>5.0000000000000001e-03</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:E51" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="C2:C51"/>
+  </sortState>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" width="11.140625"/>
     <col bestFit="1" min="2" max="2" width="28.140625"/>
     <col customWidth="1" hidden="1" min="3" max="4" width="0"/>
     <col customWidth="1" hidden="1" min="5" max="5" width="8.140625"/>
@@ -1076,25 +1968,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" ht="14.25">
@@ -1102,13 +1994,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="E2" s="3">
         <v>3.0962634061024067e-02</v>
@@ -1125,16 +2017,16 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="E3" s="3">
         <v>3.1424819508328677e-02</v>
@@ -1151,16 +2043,16 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3">
         <v>2.4805671292413338e-02</v>
@@ -1177,16 +2069,16 @@
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3">
         <v>3.052356663662641e-02</v>
@@ -1203,16 +2095,16 @@
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="E6" s="3">
         <v>2.8815825506352546e-02</v>
@@ -1229,16 +2121,16 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E7" s="3">
         <v>2.0270896772761948e-02</v>
@@ -1255,16 +2147,16 @@
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
         <v>1.8889675597916298e-02</v>
@@ -1281,16 +2173,16 @@
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="E9" s="3">
         <v>7.2822559543963706e-03</v>
@@ -1307,16 +2199,16 @@
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="E10" s="3">
         <v>3.0292282855981574e-02</v>
@@ -1333,16 +2225,16 @@
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3">
         <v>2.7132928626070054e-02</v>
@@ -1359,16 +2251,16 @@
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="E12" s="3">
         <v>2.339145668227165e-02</v>
@@ -1385,16 +2277,16 @@
     </row>
     <row r="13" ht="14.25">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="E13" s="3">
         <v>2.7534380619805943e-02</v>
@@ -1411,16 +2303,16 @@
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="E14" s="3">
         <v>2.1699035796102186e-02</v>
@@ -1437,16 +2329,16 @@
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="E15" s="3">
         <v>2.4002268007459516e-02</v>
@@ -1463,16 +2355,16 @@
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="E16" s="3">
         <v>1.20868276388375e-02</v>
@@ -1489,16 +2381,16 @@
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3">
         <v>2.5899480754485733e-02</v>
@@ -1515,16 +2407,16 @@
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="E18" s="3">
         <v>2.2745125426314856e-02</v>
@@ -1541,16 +2433,16 @@
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="E19" s="3">
         <v>1.5924694893597595e-02</v>
@@ -1567,16 +2459,16 @@
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="E20" s="3">
         <v>3.3426578117660671e-02</v>
@@ -1593,16 +2485,16 @@
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E21" s="3">
         <v>2.9899510066812067e-02</v>
@@ -1619,16 +2511,16 @@
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="1" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="E22" s="3">
         <v>1.1098145244875833e-02</v>
@@ -1645,16 +2537,16 @@
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="1" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E23" s="3">
         <v>2.2837587441750774e-02</v>
@@ -1671,16 +2563,16 @@
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="1" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="E24" s="3">
         <v>1.5797567148739283e-02</v>
@@ -1697,16 +2589,16 @@
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="E25" s="3">
         <v>2.2741899265868077e-02</v>
@@ -1726,13 +2618,13 @@
         <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="E26" s="3">
         <v>2.2141646921020147e-02</v>
@@ -1749,16 +2641,16 @@
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="1" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="E27" s="3">
         <v>2.2977675579801321e-02</v>
@@ -1775,16 +2667,16 @@
     </row>
     <row r="28" ht="14.25">
       <c r="A28" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="E28" s="3">
         <v>2.3529974058399253e-02</v>
@@ -1801,16 +2693,16 @@
     </row>
     <row r="29" ht="14.25">
       <c r="A29" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E29" s="3">
         <v>2.4403565241898753e-02</v>
@@ -1827,16 +2719,16 @@
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="1" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="E30" s="3">
         <v>2.7878086561949296e-02</v>
@@ -1853,16 +2745,16 @@
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E31" s="3">
         <v>1.9233893028455604e-02</v>
@@ -1879,16 +2771,16 @@
     </row>
     <row r="32" ht="14.25">
       <c r="A32" s="1" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E32" s="3">
         <v>1.7551131962024825e-02</v>
@@ -1905,16 +2797,16 @@
     </row>
     <row r="33" ht="14.25">
       <c r="A33" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E33" s="3">
         <v>1.8473428879071552e-02</v>
@@ -1931,16 +2823,16 @@
     </row>
     <row r="34" ht="14.25">
       <c r="A34" s="1" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E34" s="3">
         <v>2.0108078785986434e-02</v>
@@ -1957,16 +2849,16 @@
     </row>
     <row r="35" ht="14.25">
       <c r="A35" s="1" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E35" s="3">
         <v>2.2384977711044654e-02</v>
@@ -1983,16 +2875,16 @@
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E36" s="3">
         <v>1.9519654650856855e-02</v>
@@ -2009,16 +2901,16 @@
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="1" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E37" s="3">
         <v>2.9175859286267512e-02</v>
@@ -2035,16 +2927,16 @@
     </row>
     <row r="38" ht="14.25">
       <c r="A38" s="1" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="E38" s="3">
         <v>1.782528600939615e-02</v>
@@ -2061,16 +2953,16 @@
     </row>
     <row r="39" ht="14.25">
       <c r="A39" s="1" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="E39" s="3">
         <v>1.3998904335095513e-02</v>
@@ -2087,16 +2979,16 @@
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="1" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E40" s="3">
         <v>1.2198249976658535e-02</v>
@@ -2113,16 +3005,16 @@
     </row>
     <row r="41" ht="14.25">
       <c r="A41" s="1" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E41" s="3">
         <v>1.6607913200733296e-02</v>
@@ -2139,16 +3031,16 @@
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E42" s="3">
         <v>6.6293257797714628e-03</v>
@@ -2165,16 +3057,16 @@
     </row>
     <row r="43" ht="14.25">
       <c r="A43" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E43" s="3">
         <v>1.3266001122805918e-02</v>
@@ -2191,16 +3083,16 @@
     </row>
     <row r="44" ht="14.25">
       <c r="A44" s="1" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="E44" s="3">
         <v>1.9796194208153834e-02</v>
@@ -2217,16 +3109,16 @@
     </row>
     <row r="45" ht="14.25">
       <c r="A45" s="1" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E45" s="3">
         <v>1.8712999208829139e-02</v>
@@ -2243,16 +3135,16 @@
     </row>
     <row r="46" ht="14.25">
       <c r="A46" s="1" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="E46" s="3">
         <v>1.4464766120519525e-02</v>
@@ -2269,16 +3161,16 @@
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="1" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E47" s="3">
         <v>1.7331331276876891e-02</v>
@@ -2295,16 +3187,16 @@
     </row>
     <row r="48" ht="14.25">
       <c r="A48" s="1" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="E48" s="3">
         <v>1.2657258221059748e-02</v>
@@ -2321,16 +3213,16 @@
     </row>
     <row r="49" ht="14.25">
       <c r="A49" s="1" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="E49" s="3">
         <v>8.6036655312242694e-03</v>
@@ -2347,16 +3239,16 @@
     </row>
     <row r="50" ht="14.25">
       <c r="A50" s="1" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E50" s="3">
         <v>0</v>
@@ -2373,16 +3265,16 @@
     </row>
     <row r="51" ht="14.25">
       <c r="A51" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E51" s="3">
         <v>1.0450184256466147e-03</v>
@@ -2409,7 +3301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -2418,10 +3310,10 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" ht="14.25">
@@ -2434,7 +3326,7 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>2.8352089725409115e-02</v>
@@ -2442,7 +3334,7 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="B4">
         <v>2.2524399757407488e-02</v>
@@ -2450,7 +3342,7 @@
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B5">
         <v>1.0542889211305421e-02</v>
@@ -2458,7 +3350,7 @@
     </row>
     <row r="6" ht="14.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="B6">
         <v>2.3089961559775309e-02</v>
@@ -2466,7 +3358,7 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="B7">
         <v>2.6458242311494837e-02</v>
@@ -2474,7 +3366,7 @@
     </row>
     <row r="8" ht="14.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>2.0829207947211357e-02</v>
@@ -2482,7 +3374,7 @@
     </row>
     <row r="9" ht="14.25">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>2.050731937345103e-02</v>
@@ -2490,7 +3382,7 @@
     </row>
     <row r="10" ht="14.25">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>2.1235989867584643e-02</v>
@@ -2498,7 +3390,7 @@
     </row>
     <row r="11" ht="14.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B11">
         <v>1.7824338577568374e-02</v>
@@ -2506,7 +3398,7 @@
     </row>
     <row r="12" ht="14.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B12">
         <v>2.8788334737737748e-02</v>
@@ -2514,7 +3406,7 @@
     </row>
     <row r="13" ht="14.25">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="B13">
         <v>1.5990350090742338e-02</v>
@@ -2522,7 +3414,7 @@
     </row>
     <row r="14" ht="14.25">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>1.9170539093880154e-02</v>
@@ -2530,7 +3422,7 @@
     </row>
     <row r="15" ht="14.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="B15">
         <v>2.245773102572042e-02</v>
@@ -2538,7 +3430,7 @@
     </row>
     <row r="16" ht="14.25">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="B16">
         <v>1.2302146512128026e-02</v>
@@ -2546,7 +3438,7 @@
     </row>
     <row r="17" ht="14.25">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="B17">
         <v>1.4985482296935235e-02</v>
@@ -2554,7 +3446,7 @@
     </row>
     <row r="18" ht="14.25">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B18">
         <v>1.9797141836327435e-02</v>
@@ -2562,7 +3454,7 @@
     </row>
     <row r="19" ht="14.25">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B19">
         <v>6.4675684276815498e-03</v>
@@ -2570,7 +3462,7 @@
     </row>
     <row r="20" ht="14.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>3.4702113934566049e-02</v>
@@ -2578,7 +3470,7 @@
     </row>
     <row r="21" ht="14.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="B21">
         <v>2.1015659879092135e-02</v>
@@ -2586,7 +3478,7 @@
     </row>
     <row r="22" ht="14.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="B22">
         <v>8.0822989818199395e-03</v>
@@ -2594,7 +3486,7 @@
     </row>
     <row r="23" ht="14.25">
       <c r="A23" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B23">
         <v>1.1928486963647912e-02</v>
@@ -2602,7 +3494,7 @@
     </row>
     <row r="24" ht="14.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B24">
         <v>2.2364703842172446e-02</v>
@@ -2610,7 +3502,7 @@
     </row>
     <row r="25" ht="14.25">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="B25">
         <v>1.428142619056226e-02</v>
@@ -2618,7 +3510,7 @@
     </row>
     <row r="26" ht="14.25">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B26">
         <v>2.374164343461406e-02</v>
@@ -2626,7 +3518,7 @@
     </row>
     <row r="27" ht="14.25">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="B27">
         <v>2.0663268933527153e-02</v>
@@ -2634,7 +3526,7 @@
     </row>
     <row r="28" ht="14.25">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="B28">
         <v>2.9830450923956489e-02</v>
@@ -2642,7 +3534,7 @@
     </row>
     <row r="29" ht="14.25">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B29">
         <v>2.1298689474776509e-02</v>
@@ -2650,7 +3542,7 @@
     </row>
     <row r="30" ht="14.25">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>2.4499003248388124e-02</v>
@@ -2658,7 +3550,7 @@
     </row>
     <row r="31" ht="14.25">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="B31">
         <v>1.1879035525123142e-02</v>
@@ -2666,7 +3558,7 @@
     </row>
     <row r="32" ht="14.25">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B32">
         <v>2.4549201735994886e-02</v>
@@ -2674,7 +3566,7 @@
     </row>
     <row r="33" ht="14.25">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B33">
         <v>2.0795474461103632e-02</v>
@@ -2682,7 +3574,7 @@
     </row>
     <row r="34" ht="14.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B34">
         <v>3.206075137216953e-02</v>
@@ -2690,7 +3582,7 @@
     </row>
     <row r="35" ht="14.25">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B35">
         <v>1.9807013521645291e-02</v>
@@ -2698,7 +3590,7 @@
     </row>
     <row r="36" ht="14.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B36">
         <v>2.2136447362695606e-02</v>
@@ -2706,7 +3598,7 @@
     </row>
     <row r="37" ht="14.25">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B37">
         <v>2.1997138393839981e-02</v>
@@ -2714,7 +3606,7 @@
     </row>
     <row r="38" ht="14.25">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B38">
         <v>1.928301982771527e-02</v>
@@ -2722,7 +3614,7 @@
     </row>
     <row r="39" ht="14.25">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="B39">
         <v>1.0036131633024442e-02</v>
@@ -2730,7 +3622,7 @@
     </row>
     <row r="40" ht="14.25">
       <c r="A40" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="B40">
         <v>1.702275695273987e-02</v>
@@ -2738,7 +3630,7 @@
     </row>
     <row r="41" ht="14.25">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="B41">
         <v>2.5045730085698558e-02</v>
@@ -2754,7 +3646,7 @@
     </row>
     <row r="43" ht="14.25">
       <c r="A43" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="B43">
         <v>1.7168756771723921e-02</v>
@@ -2762,7 +3654,7 @@
     </row>
     <row r="44" ht="14.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44">
         <v>2.5833436819371197e-02</v>
@@ -2770,7 +3662,7 @@
     </row>
     <row r="45" ht="14.25">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="B45">
         <v>1.6470667885824689e-02</v>
@@ -2778,7 +3670,7 @@
     </row>
     <row r="46" ht="14.25">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B46">
         <v>1.8094071797290112e-02</v>
@@ -2786,7 +3678,7 @@
     </row>
     <row r="47" ht="14.25">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="B47">
         <v>1.4649795856304019e-02</v>
@@ -2794,7 +3686,7 @@
     </row>
     <row r="48" ht="14.25">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>1.4329526471500953e-02</v>
@@ -2802,7 +3694,7 @@
     </row>
     <row r="49" ht="14.25">
       <c r="A49" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="B49">
         <v>2.2106707876867186e-02</v>
@@ -2810,7 +3702,7 @@
     </row>
     <row r="50" ht="14.25">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="B50">
         <v>1.9901151620644191e-02</v>
@@ -2818,7 +3710,7 @@
     </row>
     <row r="51" ht="14.25">
       <c r="A51" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B51">
         <v>1.5717863088204321e-02</v>
@@ -2835,7 +3727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -2848,460 +3740,460 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>147</v>
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="7">
+        <v>128</v>
+      </c>
+      <c r="C2" s="6">
         <v>5.0000000000000003e-02</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="7">
+        <v>108</v>
+      </c>
+      <c r="C3" s="6">
         <v>4.0000000000000001e-02</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="9">
+      <c r="A4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="8">
         <v>2.9999999999999999e-02</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="A5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="8">
         <v>2.9999999999999999e-02</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="9">
+      <c r="A6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8">
         <v>2.9999999999999999e-02</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="8">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="8">
+        <v>2.9999999999999999e-02</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="B13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="8">
         <v>2.9999999999999999e-02</v>
       </c>
     </row>
-    <row r="8" ht="14.25">
-      <c r="A8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="9">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="A9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="A10" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="9">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="A11" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="8" t="s">
+    <row r="14" ht="14.25">
+      <c r="A14" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="9">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="9">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="9">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="9">
+      <c r="B14" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="8">
         <v>2.9999999999999999e-02</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="7">
+        <v>51</v>
+      </c>
+      <c r="C15" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="7">
+        <v>99</v>
+      </c>
+      <c r="C16" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="1" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="7">
+        <v>136</v>
+      </c>
+      <c r="C17" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="1" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="7">
+        <v>55</v>
+      </c>
+      <c r="C18" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="1" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C19" s="7">
+        <v>94</v>
+      </c>
+      <c r="C19" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="7">
+        <v>65</v>
+      </c>
+      <c r="C20" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="7">
+        <v>31</v>
+      </c>
+      <c r="C21" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="7">
+        <v>113</v>
+      </c>
+      <c r="C22" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="7">
+        <v>130</v>
+      </c>
+      <c r="C23" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="7">
+        <v>33</v>
+      </c>
+      <c r="C24" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="7">
+        <v>138</v>
+      </c>
+      <c r="C25" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="26" ht="14.25">
       <c r="A26" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="7">
+        <v>7</v>
+      </c>
+      <c r="C26" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="1" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="7">
+        <v>36</v>
+      </c>
+      <c r="C27" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" s="1" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="7">
+        <v>105</v>
+      </c>
+      <c r="C28" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" s="1" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="7">
+        <v>116</v>
+      </c>
+      <c r="C29" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="7">
+        <v>91</v>
+      </c>
+      <c r="C30" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="7">
+        <v>22</v>
+      </c>
+      <c r="C31" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="7">
+        <v>133</v>
+      </c>
+      <c r="C32" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="33" ht="14.25">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="7">
+        <v>58</v>
+      </c>
+      <c r="C33" s="6">
         <v>2.e-02</v>
       </c>
     </row>
     <row r="34" ht="14.25">
       <c r="A34" s="1" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" s="7">
+        <v>81</v>
+      </c>
+      <c r="C34" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="35" ht="14.25">
       <c r="A35" s="1" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35" s="7">
+        <v>76</v>
+      </c>
+      <c r="C35" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="7">
+        <v>82</v>
+      </c>
+      <c r="C36" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="1" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C37" s="7">
+        <v>78</v>
+      </c>
+      <c r="C37" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="38" ht="14.25">
       <c r="A38" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" s="7">
+        <v>125</v>
+      </c>
+      <c r="C38" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="7">
+        <v>40</v>
+      </c>
+      <c r="C39" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="7">
+        <v>102</v>
+      </c>
+      <c r="C40" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" s="7">
+        <v>45</v>
+      </c>
+      <c r="C41" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="7">
+        <v>89</v>
+      </c>
+      <c r="C42" s="6">
         <v>1.e-02</v>
       </c>
     </row>
@@ -3310,75 +4202,75 @@
         <v>83</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="7">
+        <v>86</v>
+      </c>
+      <c r="C43" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="44" ht="14.25">
       <c r="A44" s="1" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" s="7">
+        <v>53</v>
+      </c>
+      <c r="C44" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="45" ht="14.25">
       <c r="A45" s="1" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C45" s="7">
+        <v>72</v>
+      </c>
+      <c r="C45" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="46" ht="14.25">
       <c r="A46" s="1" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C46" s="7">
+        <v>62</v>
+      </c>
+      <c r="C46" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="1" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C47" s="7">
+        <v>75</v>
+      </c>
+      <c r="C47" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="48" ht="14.25">
       <c r="A48" s="1" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C48" s="7">
+        <v>42</v>
+      </c>
+      <c r="C48" s="6">
         <v>1.e-02</v>
       </c>
     </row>
     <row r="49" ht="14.25">
       <c r="A49" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
-      </c>
-      <c r="C49" s="10">
+        <v>140</v>
+      </c>
+      <c r="C49" s="9">
         <v>1.e-02</v>
       </c>
     </row>
@@ -3387,20 +4279,20 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="10">
+        <v>10</v>
+      </c>
+      <c r="C50" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="51" ht="14.25">
       <c r="A51" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C51" s="10">
+        <v>95</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="9">
         <v>0</v>
       </c>
     </row>
@@ -3417,7 +4309,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" id="{0000001B-0041-429A-9D6E-00AC007E009C}">
+          <x14:cfRule type="containsText" priority="1" id="{00960097-0034-4A2E-A68D-006800910000}">
             <xm:f>NOT(ISERROR(SEARCH("$J$5",I2)))</xm:f>
             <xm:f>$J$5</xm:f>
             <x14:dxf>
@@ -3440,7 +4332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -3461,51 +4353,51 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="F1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="E2" s="3">
         <v>3.3426578117660671e-02</v>
@@ -3534,16 +4426,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
       </c>
       <c r="E3" s="3">
         <v>3.1424819508328677e-02</v>
@@ -3575,13 +4467,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
       </c>
       <c r="E4" s="3">
         <v>3.0962634061024067e-02</v>
@@ -3610,16 +4502,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3">
         <v>3.052356663662641e-02</v>
@@ -3648,16 +4540,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="E6" s="3">
         <v>3.0292282855981574e-02</v>
@@ -3686,16 +4578,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3">
         <v>2.9899510066812067e-02</v>
@@ -3724,16 +4616,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3">
         <v>2.9175859286267512e-02</v>
@@ -3762,16 +4654,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="E9" s="3">
         <v>2.8815825506352546e-02</v>
@@ -3800,16 +4692,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3">
         <v>2.7878086561949296e-02</v>
@@ -3838,16 +4730,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="E11" s="3">
         <v>2.7534380619805943e-02</v>
@@ -3876,16 +4768,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="E12" s="3">
         <v>2.7132928626070054e-02</v>
@@ -3914,16 +4806,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3">
         <v>2.5899480754485733e-02</v>
@@ -3952,16 +4844,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3">
         <v>2.4805671292413338e-02</v>
@@ -3990,16 +4882,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E15" s="3">
         <v>2.4403565241898753e-02</v>
@@ -4028,16 +4920,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="E16" s="3">
         <v>2.4002268007459516e-02</v>
@@ -4066,16 +4958,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="E17" s="3">
         <v>2.3529974058399253e-02</v>
@@ -4104,16 +4996,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="E18" s="3">
         <v>2.339145668227165e-02</v>
@@ -4142,16 +5034,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="E19" s="3">
         <v>2.2977675579801321e-02</v>
@@ -4180,16 +5072,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E20" s="3">
         <v>2.2837587441750774e-02</v>
@@ -4218,16 +5110,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="E21" s="3">
         <v>2.2745125426314856e-02</v>
@@ -4256,16 +5148,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="E22" s="3">
         <v>2.2741899265868077e-02</v>
@@ -4294,16 +5186,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E23" s="3">
         <v>2.2384977711044654e-02</v>
@@ -4335,13 +5227,13 @@
         <v>83</v>
       </c>
       <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
         <v>84</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>86</v>
       </c>
       <c r="E24" s="3">
         <v>2.2141646921020147e-02</v>
@@ -4370,16 +5262,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="E25" s="3">
         <v>2.1699035796102186e-02</v>
@@ -4408,16 +5300,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E26" s="3">
         <v>2.0270896772761948e-02</v>
@@ -4446,16 +5338,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E27" s="3">
         <v>2.0108078785986434e-02</v>
@@ -4484,16 +5376,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="E28" s="3">
         <v>1.9796194208153834e-02</v>
@@ -4522,16 +5414,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E29" s="3">
         <v>1.9519654650856855e-02</v>
@@ -4560,16 +5452,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E30" s="3">
         <v>1.9233893028455604e-02</v>
@@ -4598,16 +5490,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
         <v>1.8889675597916298e-02</v>
@@ -4636,16 +5528,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E32" s="3">
         <v>1.8712999208829139e-02</v>
@@ -4674,16 +5566,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E33" s="3">
         <v>1.8473428879071552e-02</v>
@@ -4712,16 +5604,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="E34" s="3">
         <v>1.782528600939615e-02</v>
@@ -4750,16 +5642,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E35" s="3">
         <v>1.7551131962024825e-02</v>
@@ -4788,16 +5680,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E36" s="3">
         <v>1.7331331276876891e-02</v>
@@ -4826,16 +5718,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E37" s="3">
         <v>1.6607913200733296e-02</v>
@@ -4864,16 +5756,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="E38" s="3">
         <v>1.5924694893597595e-02</v>
@@ -4902,16 +5794,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="E39" s="3">
         <v>1.5797567148739283e-02</v>
@@ -4940,16 +5832,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="E40" s="3">
         <v>1.4464766120519525e-02</v>
@@ -4978,16 +5870,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="E41" s="3">
         <v>1.3998904335095513e-02</v>
@@ -5016,16 +5908,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E42" s="3">
         <v>1.3266001122805918e-02</v>
@@ -5054,16 +5946,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D43" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="E43" s="3">
         <v>1.2657258221059748e-02</v>
@@ -5092,16 +5984,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E44" s="3">
         <v>1.2198249976658535e-02</v>
@@ -5130,16 +6022,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="E45" s="3">
         <v>1.20868276388375e-02</v>
@@ -5168,16 +6060,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="E46" s="3">
         <v>1.1098145244875833e-02</v>
@@ -5206,16 +6098,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="E47" s="3">
         <v>8.6036655312242694e-03</v>
@@ -5244,16 +6136,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="E48" s="3">
         <v>7.2822559543963706e-03</v>
@@ -5282,16 +6174,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E49" s="3">
         <v>6.6293257797714628e-03</v>
@@ -5320,16 +6212,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E50" s="3">
         <v>1.0450184256466147e-03</v>
@@ -5358,16 +6250,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E51" s="3">
         <v>0</v>
@@ -5407,7 +6299,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{001100EF-00B9-481D-8AEA-00C500DB0049}">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{00A100CD-00F2-4C19-8585-00DD00000085}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5424,7 +6316,7 @@
           <xm:sqref>G2:G51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{003000DB-0059-4520-9FCE-00FC009E0002}">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{00070091-00C2-4168-A822-009B001B004F}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5441,7 +6333,7 @@
           <xm:sqref>H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{00B300D8-006A-4120-8960-00BF008F00EF}">
+          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{00CF00D4-006C-4C62-BD21-00B500F70072}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5458,7 +6350,7 @@
           <xm:sqref>G2:G51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{0035009E-00B1-4A9F-9D61-008E003A00D6}">
+          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{00CC00AE-00DE-4374-B4C7-001E005E00F2}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5475,7 +6367,7 @@
           <xm:sqref>H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" id="{0056009E-0089-4728-B97E-00C000DD00E3}">
+          <x14:cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" id="{003200B1-0080-42CD-BBED-002B006D009C}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -5492,7 +6384,7 @@
           <xm:sqref>J2:J51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="lessThan" id="{00F800A9-0012-4AB4-A65B-009700D200D0}">
+          <x14:cfRule type="cellIs" priority="7" operator="lessThan" id="{007700E3-00A3-4343-92ED-00DE00CB006F}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -5509,7 +6401,7 @@
           <xm:sqref>J2:J51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" id="{0008004A-005C-4276-BF6E-0074009B0015}">
+          <x14:cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" id="{004200FC-00CA-4D22-A078-00F500EC007D}">
             <xm:f>1</xm:f>
             <x14:dxf>
               <font>
@@ -5526,7 +6418,7 @@
           <xm:sqref>K2:K51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{008C00C9-0076-4899-B24B-006E00670035}">
+          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{009700F1-00EE-4215-AEB1-006500A700B9}">
             <xm:f>1</xm:f>
             <x14:dxf>
               <font>
@@ -5543,7 +6435,7 @@
           <xm:sqref>K2:K51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{00B3007C-001B-4E6B-A469-0021008600EC}">
+          <x14:cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" id="{002E0065-0003-4EA9-AF05-003100220079}">
             <xm:f>0.30</xm:f>
             <x14:dxf>
               <font>
@@ -5560,7 +6452,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" id="{0040008A-00BB-4F57-A864-00AC007500D1}">
+          <x14:cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" id="{00E300CB-00D1-40BB-9AC4-0044008E005E}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -5577,7 +6469,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" id="{008C0089-00B0-43A9-A493-00FE00B000DB}">
+          <x14:cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" id="{003B0064-00EF-42CB-9731-008700560065}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -5594,7 +6486,7 @@
           <xm:sqref>L2:L51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{0067006C-00AD-482D-A4E4-001300A200F2}">
+          <x14:cfRule type="cellIs" priority="1" operator="lessThan" id="{00860006-003E-4A4C-A0CE-006900A50071}">
             <xm:f>0.20</xm:f>
             <x14:dxf>
               <font>
@@ -5616,7 +6508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -5636,51 +6528,51 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
+        <v>142</v>
       </c>
       <c r="G1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3">
         <v>3.2980211092431065e-02</v>
@@ -5709,16 +6601,16 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="E3" s="3">
         <v>2.3065267907863542e-02</v>
@@ -5747,16 +6639,16 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E4" s="3">
         <v>1.7112096763365787e-02</v>
@@ -5785,16 +6677,16 @@
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E5" s="3">
         <v>1.5125366783840714e-02</v>
@@ -5823,16 +6715,16 @@
     </row>
     <row r="6" ht="14.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="E6" s="3">
         <v>4.0381665566972993e-02</v>
@@ -5861,16 +6753,16 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3">
         <v>1.7185950226781169e-02</v>
@@ -5899,16 +6791,16 @@
     </row>
     <row r="8" ht="14.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="E8" s="3">
         <v>2.516751532459971e-02</v>
@@ -5937,16 +6829,16 @@
     </row>
     <row r="9" ht="14.25">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E9" s="3">
         <v>6.2643734901931362e-03</v>
@@ -5975,16 +6867,16 @@
     </row>
     <row r="10" ht="14.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E10" s="3">
         <v>1.8351501260092357e-02</v>
@@ -6013,16 +6905,16 @@
     </row>
     <row r="11" ht="14.25">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E11" s="3">
         <v>2.196489175314608e-02</v>
@@ -6051,16 +6943,16 @@
     </row>
     <row r="12" ht="14.25">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3">
         <v>2.1034030942693117e-02</v>
@@ -6089,16 +6981,16 @@
     </row>
     <row r="13" ht="14.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E13" s="3">
         <v>1.9691696764384856e-02</v>
@@ -6127,16 +7019,16 @@
     </row>
     <row r="14" ht="14.25">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3">
         <v>5.6934558426866471e-03</v>
@@ -6165,16 +7057,16 @@
     </row>
     <row r="15" ht="14.25">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E15" s="3">
         <v>2.1612848078154535e-02</v>
@@ -6203,16 +7095,16 @@
     </row>
     <row r="16" ht="14.25">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3">
         <v>1.5623604119377809e-02</v>
@@ -6241,16 +7133,16 @@
     </row>
     <row r="17" ht="14.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="E17" s="3">
         <v>3.1347650966415792e-02</v>
@@ -6279,16 +7171,16 @@
     </row>
     <row r="18" ht="14.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="E18" s="3">
         <v>1.5035036820334224e-02</v>
@@ -6317,16 +7209,16 @@
     </row>
     <row r="19" ht="14.25">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="E19" s="3">
         <v>2.8580424264704501e-02</v>
@@ -6355,16 +7247,16 @@
     </row>
     <row r="20" ht="14.25">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E20" s="3">
         <v>2.8358472898339484e-03</v>
@@ -6393,16 +7285,16 @@
     </row>
     <row r="21" ht="14.25">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E21" s="3">
         <v>1.3359628471997327e-02</v>
@@ -6431,16 +7323,16 @@
     </row>
     <row r="22" ht="14.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E22" s="3">
         <v>3.2448787056903745e-02</v>
@@ -6469,16 +7361,16 @@
     </row>
     <row r="23" ht="14.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="E23" s="3">
         <v>3.1078663771106518e-02</v>
@@ -6507,16 +7399,16 @@
     </row>
     <row r="24" ht="14.25">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E24" s="3">
         <v>4.0313637453391955e-02</v>
@@ -6545,16 +7437,16 @@
     </row>
     <row r="25" ht="14.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E25" s="3">
         <v>1.4947812995714384e-02</v>
@@ -6583,16 +7475,16 @@
     </row>
     <row r="26" ht="14.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E26" s="3">
         <v>4.3723700398078769e-02</v>
@@ -6621,16 +7513,16 @@
     </row>
     <row r="27" ht="14.25">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E27" s="3">
         <v>3.0800114740260325e-02</v>
@@ -6659,16 +7551,16 @@
     </row>
     <row r="28" ht="14.25">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E28" s="3">
         <v>1.866780880211432e-02</v>
@@ -6697,16 +7589,16 @@
     </row>
     <row r="29" ht="14.25">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="E29" s="3">
         <v>1.0053069455554359e-02</v>
@@ -6735,16 +7627,16 @@
     </row>
     <row r="30" ht="14.25">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="E30" s="3">
         <v>2.3656316327064039e-02</v>
@@ -6773,16 +7665,16 @@
     </row>
     <row r="31" ht="14.25">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="E31" s="3">
         <v>7.8078953359519308e-03</v>
@@ -6811,16 +7703,16 @@
     </row>
     <row r="32" ht="14.25">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E32" s="3">
         <v>1.3530475135421131e-02</v>
@@ -6849,16 +7741,16 @@
     </row>
     <row r="33" ht="14.25">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E33" s="3">
         <v>1.9706989794432826e-02</v>
@@ -6887,16 +7779,16 @@
     </row>
     <row r="34" ht="14.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E34" s="3">
         <v>2.327816597403403e-02</v>
@@ -6928,13 +7820,13 @@
         <v>83</v>
       </c>
       <c r="B35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" t="s">
         <v>84</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>85</v>
-      </c>
-      <c r="D35" t="s">
-        <v>86</v>
       </c>
       <c r="E35" s="3">
         <v>1.7371504943138679e-03</v>
@@ -6963,16 +7855,16 @@
     </row>
     <row r="36" ht="14.25">
       <c r="A36" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="E36" s="3">
         <v>1.6947215311778032e-02</v>
@@ -7001,16 +7893,16 @@
     </row>
     <row r="37" ht="14.25">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E37" s="3">
         <v>6.7689674834389112e-03</v>
@@ -7039,16 +7931,16 @@
     </row>
     <row r="38" ht="14.25">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="E38" s="3">
         <v>2.5669876319742841e-02</v>
@@ -7077,16 +7969,16 @@
     </row>
     <row r="39" ht="14.25">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E39" s="3">
         <v>0</v>
@@ -7115,16 +8007,16 @@
     </row>
     <row r="40" ht="14.25">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="E40" s="3">
         <v>3.4903903127292697e-02</v>
@@ -7156,13 +8048,13 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E41" s="3">
         <v>2.2170108023531771e-02</v>
@@ -7191,16 +8083,16 @@
     </row>
     <row r="42" ht="14.25">
       <c r="A42" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E42" s="3">
         <v>1.204275820288234e-02</v>
@@ -7229,16 +8121,16 @@
     </row>
     <row r="43" ht="14.25">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E43" s="3">
         <v>4.104901444017256e-02</v>
@@ -7267,16 +8159,16 @@
     </row>
     <row r="44" ht="14.25">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D44" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E44" s="3">
         <v>2.8095910154655214e-02</v>
@@ -7305,16 +8197,16 @@
     </row>
     <row r="45" ht="14.25">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E45" s="3">
         <v>1.0521185108879184e-02</v>
@@ -7343,16 +8235,16 @@
     </row>
     <row r="46" ht="14.25">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D46" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="E46" s="3">
         <v>2.3374000188728025e-02</v>
@@ -7381,16 +8273,16 @@
     </row>
     <row r="47" ht="14.25">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E47" s="3">
         <v>1.2762914852215508e-02</v>
@@ -7419,16 +8311,16 @@
     </row>
     <row r="48" ht="14.25">
       <c r="A48" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="E48" s="3">
         <v>1.4175317216634876e-02</v>
@@ -7457,16 +8349,16 @@
     </row>
     <row r="49" ht="14.25">
       <c r="A49" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E49" s="3">
         <v>4.9786131509862545e-03</v>
@@ -7495,16 +8387,16 @@
     </row>
     <row r="50" ht="14.25">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="E50" s="3">
         <v>2.2001586031867262e-02</v>
@@ -7533,16 +8425,16 @@
     </row>
     <row r="51" ht="14.25">
       <c r="A51" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E51" s="3">
         <v>2.0374978922983133e-02</v>
@@ -7570,7 +8462,7 @@
       </c>
     </row>
     <row r="52" ht="14.25">
-      <c r="F52" s="11"/>
+      <c r="F52" s="10"/>
     </row>
   </sheetData>
   <sortState ref="A2:L51" columnSort="0">
@@ -7583,7 +8475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
+++ b/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/safishajjouz/GitHub/QuantitativePortfolioManagement/myPortfolioManagement/MeteoraGlobalEquityFund/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD083167-F5CE-CE43-AF07-B01B26630E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DA1CAB-69D5-D74A-8717-4D75A703DA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="500" windowWidth="29940" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet5" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet4" sheetId="3" r:id="rId3"/>
-    <sheet name="Portfolio_Stocks" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet6" sheetId="8" r:id="rId7"/>
-    <sheet name="BBPTACShadowWks0001" sheetId="7" state="hidden" r:id="rId8"/>
+    <sheet name="all_stocks" sheetId="1" r:id="rId1"/>
+    <sheet name="Pie_Global_Meteora" sheetId="9" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="3" r:id="rId4"/>
+    <sheet name="Portfolio_Stocks" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet6" sheetId="8" r:id="rId8"/>
+    <sheet name="BBPTACShadowWks0001" sheetId="7" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="178">
   <si>
     <t>YahooTicker</t>
   </si>
@@ -630,10 +631,10 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2030,6 +2031,1024 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3BB519-E36C-B644-8760-AAFC418C0AF6}">
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2">
+        <v>0.02</v>
+      </c>
+      <c r="F2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3">
+        <v>0.02</v>
+      </c>
+      <c r="F3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4">
+        <v>0.02</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5">
+        <v>0.01</v>
+      </c>
+      <c r="F5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6">
+        <v>0.02</v>
+      </c>
+      <c r="F6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7">
+        <v>0.01</v>
+      </c>
+      <c r="F7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>0.04</v>
+      </c>
+      <c r="F8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9">
+        <v>0.02</v>
+      </c>
+      <c r="F9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>0.04</v>
+      </c>
+      <c r="F10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11">
+        <v>0.03</v>
+      </c>
+      <c r="F11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15">
+        <v>0.02</v>
+      </c>
+      <c r="F15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16">
+        <v>0.02</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17">
+        <v>0.02</v>
+      </c>
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18">
+        <v>0.02</v>
+      </c>
+      <c r="F18" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21">
+        <v>0.01</v>
+      </c>
+      <c r="F21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22">
+        <v>0.02</v>
+      </c>
+      <c r="F22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23">
+        <v>0.01</v>
+      </c>
+      <c r="F23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25">
+        <v>0.02</v>
+      </c>
+      <c r="F25" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26">
+        <v>0.02</v>
+      </c>
+      <c r="F26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28">
+        <v>0.03</v>
+      </c>
+      <c r="F28" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30">
+        <v>0.03</v>
+      </c>
+      <c r="F30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31">
+        <v>0.04</v>
+      </c>
+      <c r="F31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32">
+        <v>0.03</v>
+      </c>
+      <c r="F32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F33" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34">
+        <v>0.02</v>
+      </c>
+      <c r="F34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35">
+        <v>0.01</v>
+      </c>
+      <c r="F35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36">
+        <v>0.01</v>
+      </c>
+      <c r="F36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>127</v>
+      </c>
+      <c r="D37" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37">
+        <v>0.02</v>
+      </c>
+      <c r="F37" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38">
+        <v>0.02</v>
+      </c>
+      <c r="F38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41">
+        <v>0.02</v>
+      </c>
+      <c r="F41" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F42" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43">
+        <v>0.02</v>
+      </c>
+      <c r="F43" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F45" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" t="s">
+        <v>115</v>
+      </c>
+      <c r="D46" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46">
+        <v>0.02</v>
+      </c>
+      <c r="F46" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D48" t="s">
+        <v>120</v>
+      </c>
+      <c r="E48">
+        <v>0.02</v>
+      </c>
+      <c r="F48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" t="s">
+        <v>86</v>
+      </c>
+      <c r="E50">
+        <v>0.02</v>
+      </c>
+      <c r="F50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3378,7 +4397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3803,7 +4822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4406,7 +5425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -6408,7 +7427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8374,7 +9393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2965CCB6-C2E0-E64A-ACF1-C6FF1A168B7D}">
   <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9545,7 +10564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
+++ b/myPortfolioManagement/MeteoraGlobalEquityFund/Data/stock_screening.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/safishajjouz/GitHub/QuantitativePortfolioManagement/myPortfolioManagement/MeteoraGlobalEquityFund/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DA1CAB-69D5-D74A-8717-4D75A703DA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0CCEB48-0000-7445-83B6-B117EE7AAC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="500" windowWidth="29940" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="179">
   <si>
     <t>YahooTicker</t>
   </si>
@@ -575,6 +575,9 @@
   </si>
   <si>
     <t>AZNl</t>
+  </si>
+  <si>
+    <t>yahooTicker</t>
   </si>
 </sst>
 </file>
@@ -596,12 +599,14 @@
       <sz val="11"/>
       <color indexed="2"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -629,7 +634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -640,12 +645,24 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF92D050"/>
@@ -676,39 +693,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF92D050"/>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -753,6 +737,28 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF92D050"/>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1002,8 +1008,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -7385,18 +7391,18 @@
     <sortCondition ref="E2:E51"/>
   </sortState>
   <conditionalFormatting sqref="G2:H51">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J51">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="greaterThanOrEqual">
       <formula>0.3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7409,17 +7415,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L51">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThanOrEqual">
+      <formula>0.3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThanOrEqual">
       <formula>0.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThanOrEqual">
       <formula>0.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThanOrEqual">
-      <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
